--- a/database/event/6863/event_6863_evp_summary.xlsx
+++ b/database/event/6863/event_6863_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>10.8434</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>8.2142</v>
       </c>
       <c r="D2" t="n">
         <v>3.9591</v>
@@ -545,7 +545,7 @@
         <v>10.6404</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>8.060499999999999</v>
       </c>
       <c r="D3" t="n">
         <v>3.8771</v>
@@ -591,7 +591,7 @@
         <v>8.968</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>6.7936</v>
       </c>
       <c r="D4" t="n">
         <v>3.2015</v>
@@ -637,7 +637,7 @@
         <v>7.8089</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>5.9155</v>
       </c>
       <c r="D5" t="n">
         <v>2.7333</v>
@@ -683,7 +683,7 @@
         <v>7.5286</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>5.7032</v>
       </c>
       <c r="D6" t="n">
         <v>2.62</v>
@@ -729,7 +729,7 @@
         <v>7.049</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>5.3399</v>
       </c>
       <c r="D7" t="n">
         <v>2.4263</v>
@@ -775,7 +775,7 @@
         <v>6.381</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>4.8338</v>
       </c>
       <c r="D8" t="n">
         <v>2.1564</v>
@@ -821,7 +821,7 @@
         <v>6.1413</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>4.6522</v>
       </c>
       <c r="D9" t="n">
         <v>2.0596</v>
@@ -867,7 +867,7 @@
         <v>6.1022</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>4.6226</v>
       </c>
       <c r="D10" t="n">
         <v>2.0438</v>
@@ -913,7 +913,7 @@
         <v>5.491</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>4.1596</v>
       </c>
       <c r="D11" t="n">
         <v>1.7969</v>
@@ -959,7 +959,7 @@
         <v>5.3528</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>4.0549</v>
       </c>
       <c r="D12" t="n">
         <v>1.7411</v>
@@ -1005,7 +1005,7 @@
         <v>5.2736</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>3.9949</v>
       </c>
       <c r="D13" t="n">
         <v>1.7091</v>
@@ -1051,7 +1051,7 @@
         <v>5.2071</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>3.9446</v>
       </c>
       <c r="D14" t="n">
         <v>1.6822</v>
@@ -1097,7 +1097,7 @@
         <v>5.1974</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>3.9372</v>
       </c>
       <c r="D15" t="n">
         <v>1.6783</v>
@@ -1143,7 +1143,7 @@
         <v>4.9256</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3.7313</v>
       </c>
       <c r="D16" t="n">
         <v>1.5685</v>
@@ -1189,7 +1189,7 @@
         <v>4.9184</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>3.7259</v>
       </c>
       <c r="D17" t="n">
         <v>1.5656</v>
@@ -1235,7 +1235,7 @@
         <v>4.8429</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>3.6687</v>
       </c>
       <c r="D18" t="n">
         <v>1.5351</v>
@@ -1281,7 +1281,7 @@
         <v>4.2995</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>3.257</v>
       </c>
       <c r="D19" t="n">
         <v>1.3155</v>
@@ -1327,7 +1327,7 @@
         <v>4.1505</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>3.1441</v>
       </c>
       <c r="D20" t="n">
         <v>1.2553</v>
@@ -1373,7 +1373,7 @@
         <v>4.112</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>3.115</v>
       </c>
       <c r="D21" t="n">
         <v>1.2398</v>
@@ -1419,7 +1419,7 @@
         <v>4.0728</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>3.0853</v>
       </c>
       <c r="D22" t="n">
         <v>1.224</v>
@@ -1465,7 +1465,7 @@
         <v>3.9284</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>2.9759</v>
       </c>
       <c r="D23" t="n">
         <v>1.1656</v>
@@ -1511,7 +1511,7 @@
         <v>3.9089</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>2.9611</v>
       </c>
       <c r="D24" t="n">
         <v>1.1577</v>
@@ -1557,7 +1557,7 @@
         <v>3.6819</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>2.7892</v>
       </c>
       <c r="D25" t="n">
         <v>1.066</v>
@@ -1603,7 +1603,7 @@
         <v>3.3408</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>2.5308</v>
       </c>
       <c r="D26" t="n">
         <v>0.9282</v>
@@ -1649,7 +1649,7 @@
         <v>3.3158</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>2.5118</v>
       </c>
       <c r="D27" t="n">
         <v>0.9181</v>
@@ -1695,7 +1695,7 @@
         <v>3.3069</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>2.5051</v>
       </c>
       <c r="D28" t="n">
         <v>0.9146</v>
@@ -1741,7 +1741,7 @@
         <v>3.1988</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>2.4232</v>
       </c>
       <c r="D29" t="n">
         <v>0.8709</v>
@@ -1787,7 +1787,7 @@
         <v>3.1888</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>2.4156</v>
       </c>
       <c r="D30" t="n">
         <v>0.8668</v>
@@ -1833,7 +1833,7 @@
         <v>3.1497</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>2.386</v>
       </c>
       <c r="D31" t="n">
         <v>0.851</v>
@@ -1879,7 +1879,7 @@
         <v>3.1248</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>2.3671</v>
       </c>
       <c r="D32" t="n">
         <v>0.841</v>
@@ -1925,7 +1925,7 @@
         <v>3.0287</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>2.2943</v>
       </c>
       <c r="D33" t="n">
         <v>0.8022</v>
@@ -1971,7 +1971,7 @@
         <v>2.8797</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>2.1815</v>
       </c>
       <c r="D34" t="n">
         <v>0.742</v>
@@ -2017,7 +2017,7 @@
         <v>2.8403</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>2.1516</v>
       </c>
       <c r="D35" t="n">
         <v>0.7261</v>
@@ -2063,7 +2063,7 @@
         <v>2.7881</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>2.1121</v>
       </c>
       <c r="D36" t="n">
         <v>0.705</v>
@@ -2109,7 +2109,7 @@
         <v>2.7163</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>2.0577</v>
       </c>
       <c r="D37" t="n">
         <v>0.676</v>
@@ -2155,7 +2155,7 @@
         <v>2.7144</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>2.0563</v>
       </c>
       <c r="D38" t="n">
         <v>0.6752</v>
@@ -2201,7 +2201,7 @@
         <v>2.6917</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>2.0391</v>
       </c>
       <c r="D39" t="n">
         <v>0.666</v>
@@ -2247,7 +2247,7 @@
         <v>2.6484</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>2.0063</v>
       </c>
       <c r="D40" t="n">
         <v>0.6485</v>
@@ -2293,7 +2293,7 @@
         <v>2.5587</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>1.9383</v>
       </c>
       <c r="D41" t="n">
         <v>0.6123</v>
@@ -2339,7 +2339,7 @@
         <v>2.5429</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>1.9263</v>
       </c>
       <c r="D42" t="n">
         <v>0.6059</v>
@@ -2385,7 +2385,7 @@
         <v>2.468</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>1.8696</v>
       </c>
       <c r="D43" t="n">
         <v>0.5757</v>
@@ -2431,7 +2431,7 @@
         <v>2.4498</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>1.8558</v>
       </c>
       <c r="D44" t="n">
         <v>0.5683</v>
@@ -2477,7 +2477,7 @@
         <v>2.4086</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>1.8246</v>
       </c>
       <c r="D45" t="n">
         <v>0.5517</v>
@@ -2523,7 +2523,7 @@
         <v>2.2806</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>1.7276</v>
       </c>
       <c r="D46" t="n">
         <v>0.4999</v>
@@ -2569,7 +2569,7 @@
         <v>2.2747</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>1.7232</v>
       </c>
       <c r="D47" t="n">
         <v>0.4976</v>
@@ -2615,7 +2615,7 @@
         <v>2.2532</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>1.7069</v>
       </c>
       <c r="D48" t="n">
         <v>0.4889</v>
@@ -2661,7 +2661,7 @@
         <v>2.2364</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>1.6941</v>
       </c>
       <c r="D49" t="n">
         <v>0.4821</v>
@@ -2707,7 +2707,7 @@
         <v>2.1779</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>1.6498</v>
       </c>
       <c r="D50" t="n">
         <v>0.4585</v>
@@ -2753,7 +2753,7 @@
         <v>2.1148</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>1.602</v>
       </c>
       <c r="D51" t="n">
         <v>0.433</v>
@@ -2799,7 +2799,7 @@
         <v>2.067</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>1.5658</v>
       </c>
       <c r="D52" t="n">
         <v>0.4137</v>
@@ -2845,7 +2845,7 @@
         <v>1.8613</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="D53" t="n">
         <v>0.3306</v>
@@ -2891,7 +2891,7 @@
         <v>1.856</v>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>1.406</v>
       </c>
       <c r="D54" t="n">
         <v>0.3284</v>
@@ -2937,7 +2937,7 @@
         <v>1.8202</v>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>1.3789</v>
       </c>
       <c r="D55" t="n">
         <v>0.314</v>
@@ -2983,7 +2983,7 @@
         <v>1.8131</v>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>1.3735</v>
       </c>
       <c r="D56" t="n">
         <v>0.3111</v>
@@ -3029,7 +3029,7 @@
         <v>1.7862</v>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>1.3531</v>
       </c>
       <c r="D57" t="n">
         <v>0.3002</v>
@@ -3075,7 +3075,7 @@
         <v>1.7827</v>
       </c>
       <c r="C58" t="n">
-        <v>0</v>
+        <v>1.3505</v>
       </c>
       <c r="D58" t="n">
         <v>0.2988</v>
@@ -3121,7 +3121,7 @@
         <v>1.7406</v>
       </c>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>1.3186</v>
       </c>
       <c r="D59" t="n">
         <v>0.2818</v>
@@ -3167,7 +3167,7 @@
         <v>1.6686</v>
       </c>
       <c r="C60" t="n">
-        <v>0</v>
+        <v>1.264</v>
       </c>
       <c r="D60" t="n">
         <v>0.2527</v>
@@ -3213,7 +3213,7 @@
         <v>1.6279</v>
       </c>
       <c r="C61" t="n">
-        <v>0</v>
+        <v>1.2332</v>
       </c>
       <c r="D61" t="n">
         <v>0.2363</v>
@@ -3259,7 +3259,7 @@
         <v>1.6074</v>
       </c>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>1.2177</v>
       </c>
       <c r="D62" t="n">
         <v>0.228</v>
@@ -3305,7 +3305,7 @@
         <v>1.5408</v>
       </c>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>1.1672</v>
       </c>
       <c r="D63" t="n">
         <v>0.2011</v>
@@ -3351,7 +3351,7 @@
         <v>1.5248</v>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>1.1551</v>
       </c>
       <c r="D64" t="n">
         <v>0.1946</v>
@@ -3397,7 +3397,7 @@
         <v>1.4228</v>
       </c>
       <c r="C65" t="n">
-        <v>0</v>
+        <v>1.0778</v>
       </c>
       <c r="D65" t="n">
         <v>0.1534</v>
@@ -3443,7 +3443,7 @@
         <v>1.3909</v>
       </c>
       <c r="C66" t="n">
-        <v>0</v>
+        <v>1.0537</v>
       </c>
       <c r="D66" t="n">
         <v>0.1405</v>
@@ -3489,7 +3489,7 @@
         <v>1.3239</v>
       </c>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>1.0029</v>
       </c>
       <c r="D67" t="n">
         <v>0.1135</v>
@@ -3535,7 +3535,7 @@
         <v>1.3231</v>
       </c>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>1.0023</v>
       </c>
       <c r="D68" t="n">
         <v>0.1131</v>
@@ -3581,7 +3581,7 @@
         <v>1.274</v>
       </c>
       <c r="C69" t="n">
-        <v>0</v>
+        <v>0.9651</v>
       </c>
       <c r="D69" t="n">
         <v>0.09329999999999999</v>
@@ -3627,7 +3627,7 @@
         <v>1.2494</v>
       </c>
       <c r="C70" t="n">
-        <v>0</v>
+        <v>0.9465</v>
       </c>
       <c r="D70" t="n">
         <v>0.0834</v>
@@ -3673,7 +3673,7 @@
         <v>1.1672</v>
       </c>
       <c r="C71" t="n">
-        <v>0</v>
+        <v>0.8842</v>
       </c>
       <c r="D71" t="n">
         <v>0.0502</v>
@@ -3719,7 +3719,7 @@
         <v>1.1308</v>
       </c>
       <c r="C72" t="n">
-        <v>0</v>
+        <v>0.8566</v>
       </c>
       <c r="D72" t="n">
         <v>0.0355</v>
@@ -3765,7 +3765,7 @@
         <v>1.1238</v>
       </c>
       <c r="C73" t="n">
-        <v>0</v>
+        <v>0.8512999999999999</v>
       </c>
       <c r="D73" t="n">
         <v>0.0326</v>
@@ -3811,7 +3811,7 @@
         <v>1.1116</v>
       </c>
       <c r="C74" t="n">
-        <v>0</v>
+        <v>0.8421</v>
       </c>
       <c r="D74" t="n">
         <v>0.0277</v>
@@ -3857,7 +3857,7 @@
         <v>1.1114</v>
       </c>
       <c r="C75" t="n">
-        <v>0</v>
+        <v>0.8419</v>
       </c>
       <c r="D75" t="n">
         <v>0.0276</v>
@@ -3903,7 +3903,7 @@
         <v>1.0825</v>
       </c>
       <c r="C76" t="n">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="D76" t="n">
         <v>0.0159</v>
@@ -3949,7 +3949,7 @@
         <v>1.0726</v>
       </c>
       <c r="C77" t="n">
-        <v>0</v>
+        <v>0.8125</v>
       </c>
       <c r="D77" t="n">
         <v>0.0119</v>
@@ -3995,7 +3995,7 @@
         <v>1.0413</v>
       </c>
       <c r="C78" t="n">
-        <v>0</v>
+        <v>0.7887999999999999</v>
       </c>
       <c r="D78" t="n">
         <v>-0.0007</v>
@@ -4041,7 +4041,7 @@
         <v>1.0403</v>
       </c>
       <c r="C79" t="n">
-        <v>0</v>
+        <v>0.7881</v>
       </c>
       <c r="D79" t="n">
         <v>-0.0011</v>
@@ -4087,7 +4087,7 @@
         <v>1.0176</v>
       </c>
       <c r="C80" t="n">
-        <v>0</v>
+        <v>0.7709</v>
       </c>
       <c r="D80" t="n">
         <v>-0.0103</v>
@@ -4133,7 +4133,7 @@
         <v>1.0073</v>
       </c>
       <c r="C81" t="n">
-        <v>0</v>
+        <v>0.7631</v>
       </c>
       <c r="D81" t="n">
         <v>-0.0144</v>
@@ -4179,7 +4179,7 @@
         <v>0.9797</v>
       </c>
       <c r="C82" t="n">
-        <v>0</v>
+        <v>0.7422</v>
       </c>
       <c r="D82" t="n">
         <v>-0.0256</v>
@@ -4225,7 +4225,7 @@
         <v>0.9624</v>
       </c>
       <c r="C83" t="n">
-        <v>0</v>
+        <v>0.7291</v>
       </c>
       <c r="D83" t="n">
         <v>-0.0326</v>
@@ -4271,7 +4271,7 @@
         <v>0.9602000000000001</v>
       </c>
       <c r="C84" t="n">
-        <v>0</v>
+        <v>0.7274</v>
       </c>
       <c r="D84" t="n">
         <v>-0.0335</v>
@@ -4317,7 +4317,7 @@
         <v>0.8586</v>
       </c>
       <c r="C85" t="n">
-        <v>0</v>
+        <v>0.6504</v>
       </c>
       <c r="D85" t="n">
         <v>-0.0745</v>
@@ -4363,7 +4363,7 @@
         <v>0.7964</v>
       </c>
       <c r="C86" t="n">
-        <v>0</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="D86" t="n">
         <v>-0.09959999999999999</v>
@@ -4409,7 +4409,7 @@
         <v>0.6103</v>
       </c>
       <c r="C87" t="n">
-        <v>0</v>
+        <v>0.4623</v>
       </c>
       <c r="D87" t="n">
         <v>-0.1748</v>
@@ -4455,7 +4455,7 @@
         <v>0.5785</v>
       </c>
       <c r="C88" t="n">
-        <v>0</v>
+        <v>0.4382</v>
       </c>
       <c r="D88" t="n">
         <v>-0.1877</v>
@@ -4501,7 +4501,7 @@
         <v>0.5518</v>
       </c>
       <c r="C89" t="n">
-        <v>0</v>
+        <v>0.418</v>
       </c>
       <c r="D89" t="n">
         <v>-0.1984</v>
@@ -4547,7 +4547,7 @@
         <v>0.5442</v>
       </c>
       <c r="C90" t="n">
-        <v>0</v>
+        <v>0.4123</v>
       </c>
       <c r="D90" t="n">
         <v>-0.2015</v>
@@ -4593,7 +4593,7 @@
         <v>0.5215</v>
       </c>
       <c r="C91" t="n">
-        <v>0</v>
+        <v>0.3951</v>
       </c>
       <c r="D91" t="n">
         <v>-0.2107</v>
@@ -4639,7 +4639,7 @@
         <v>0.4842</v>
       </c>
       <c r="C92" t="n">
-        <v>0</v>
+        <v>0.3668</v>
       </c>
       <c r="D92" t="n">
         <v>-0.2258</v>
@@ -4685,7 +4685,7 @@
         <v>0.4732</v>
       </c>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>0.3585</v>
       </c>
       <c r="D93" t="n">
         <v>-0.2302</v>
@@ -4731,7 +4731,7 @@
         <v>0.4696</v>
       </c>
       <c r="C94" t="n">
-        <v>0</v>
+        <v>0.3557</v>
       </c>
       <c r="D94" t="n">
         <v>-0.2317</v>
@@ -4777,7 +4777,7 @@
         <v>0.4627</v>
       </c>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>0.3505</v>
       </c>
       <c r="D95" t="n">
         <v>-0.2344</v>
@@ -4823,7 +4823,7 @@
         <v>0.4405</v>
       </c>
       <c r="C96" t="n">
-        <v>0</v>
+        <v>0.3337</v>
       </c>
       <c r="D96" t="n">
         <v>-0.2434</v>
@@ -4869,7 +4869,7 @@
         <v>0.4294</v>
       </c>
       <c r="C97" t="n">
-        <v>0</v>
+        <v>0.3253</v>
       </c>
       <c r="D97" t="n">
         <v>-0.2479</v>
@@ -4915,7 +4915,7 @@
         <v>0.4127</v>
       </c>
       <c r="C98" t="n">
-        <v>0</v>
+        <v>0.3126</v>
       </c>
       <c r="D98" t="n">
         <v>-0.2546</v>
@@ -4961,7 +4961,7 @@
         <v>0.3956</v>
       </c>
       <c r="C99" t="n">
-        <v>0</v>
+        <v>0.2997</v>
       </c>
       <c r="D99" t="n">
         <v>-0.2615</v>
@@ -5007,7 +5007,7 @@
         <v>0.3772</v>
       </c>
       <c r="C100" t="n">
-        <v>0</v>
+        <v>0.2857</v>
       </c>
       <c r="D100" t="n">
         <v>-0.269</v>
@@ -5053,7 +5053,7 @@
         <v>0.3696</v>
       </c>
       <c r="C101" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="D101" t="n">
         <v>-0.2721</v>
@@ -5099,7 +5099,7 @@
         <v>0.3685</v>
       </c>
       <c r="C102" t="n">
-        <v>0</v>
+        <v>0.2792</v>
       </c>
       <c r="D102" t="n">
         <v>-0.2725</v>
@@ -5145,7 +5145,7 @@
         <v>0.3653</v>
       </c>
       <c r="C103" t="n">
-        <v>0</v>
+        <v>0.2767</v>
       </c>
       <c r="D103" t="n">
         <v>-0.2738</v>
@@ -5191,7 +5191,7 @@
         <v>0.3588</v>
       </c>
       <c r="C104" t="n">
-        <v>0</v>
+        <v>0.2718</v>
       </c>
       <c r="D104" t="n">
         <v>-0.2764</v>
@@ -5237,7 +5237,7 @@
         <v>0.2955</v>
       </c>
       <c r="C105" t="n">
-        <v>0</v>
+        <v>0.2239</v>
       </c>
       <c r="D105" t="n">
         <v>-0.302</v>
@@ -5283,7 +5283,7 @@
         <v>0.2794</v>
       </c>
       <c r="C106" t="n">
-        <v>0</v>
+        <v>0.2117</v>
       </c>
       <c r="D106" t="n">
         <v>-0.3085</v>
@@ -5329,7 +5329,7 @@
         <v>0.2543</v>
       </c>
       <c r="C107" t="n">
-        <v>0</v>
+        <v>0.1926</v>
       </c>
       <c r="D107" t="n">
         <v>-0.3186</v>
@@ -5375,7 +5375,7 @@
         <v>0.0644</v>
       </c>
       <c r="C108" t="n">
-        <v>0</v>
+        <v>0.0488</v>
       </c>
       <c r="D108" t="n">
         <v>-0.3953</v>
@@ -5421,7 +5421,7 @@
         <v>-0.061</v>
       </c>
       <c r="C109" t="n">
-        <v>-0</v>
+        <v>-0.0462</v>
       </c>
       <c r="D109" t="n">
         <v>-0.446</v>
@@ -5467,7 +5467,7 @@
         <v>-0.2743</v>
       </c>
       <c r="C110" t="n">
-        <v>-0</v>
+        <v>-0.2078</v>
       </c>
       <c r="D110" t="n">
         <v>-0.5322</v>
@@ -5513,7 +5513,7 @@
         <v>-0.3032</v>
       </c>
       <c r="C111" t="n">
-        <v>-0</v>
+        <v>-0.2297</v>
       </c>
       <c r="D111" t="n">
         <v>-0.5438</v>
@@ -5559,7 +5559,7 @@
         <v>-0.3234</v>
       </c>
       <c r="C112" t="n">
-        <v>-0</v>
+        <v>-0.245</v>
       </c>
       <c r="D112" t="n">
         <v>-0.552</v>
@@ -5605,7 +5605,7 @@
         <v>-0.3507</v>
       </c>
       <c r="C113" t="n">
-        <v>-0</v>
+        <v>-0.2657</v>
       </c>
       <c r="D113" t="n">
         <v>-0.5629999999999999</v>
@@ -5651,7 +5651,7 @@
         <v>-0.3856</v>
       </c>
       <c r="C114" t="n">
-        <v>-0</v>
+        <v>-0.2921</v>
       </c>
       <c r="D114" t="n">
         <v>-0.5770999999999999</v>
@@ -5697,7 +5697,7 @@
         <v>-0.4128</v>
       </c>
       <c r="C115" t="n">
-        <v>-0</v>
+        <v>-0.3127</v>
       </c>
       <c r="D115" t="n">
         <v>-0.5881</v>
@@ -5743,7 +5743,7 @@
         <v>-0.4153</v>
       </c>
       <c r="C116" t="n">
-        <v>-0</v>
+        <v>-0.3146</v>
       </c>
       <c r="D116" t="n">
         <v>-0.5891</v>
@@ -5789,7 +5789,7 @@
         <v>-0.4232</v>
       </c>
       <c r="C117" t="n">
-        <v>-0</v>
+        <v>-0.3206</v>
       </c>
       <c r="D117" t="n">
         <v>-0.5923</v>
@@ -5835,7 +5835,7 @@
         <v>-0.4379</v>
       </c>
       <c r="C118" t="n">
-        <v>-0</v>
+        <v>-0.3317</v>
       </c>
       <c r="D118" t="n">
         <v>-0.5983000000000001</v>
@@ -5881,7 +5881,7 @@
         <v>-0.4774</v>
       </c>
       <c r="C119" t="n">
-        <v>-0</v>
+        <v>-0.3616</v>
       </c>
       <c r="D119" t="n">
         <v>-0.6142</v>
@@ -5927,7 +5927,7 @@
         <v>-0.4972</v>
       </c>
       <c r="C120" t="n">
-        <v>-0</v>
+        <v>-0.3766</v>
       </c>
       <c r="D120" t="n">
         <v>-0.6222</v>
@@ -5973,7 +5973,7 @@
         <v>-0.5616</v>
       </c>
       <c r="C121" t="n">
-        <v>-0</v>
+        <v>-0.4254</v>
       </c>
       <c r="D121" t="n">
         <v>-0.6482</v>
@@ -6019,7 +6019,7 @@
         <v>-0.6059</v>
       </c>
       <c r="C122" t="n">
-        <v>-0</v>
+        <v>-0.459</v>
       </c>
       <c r="D122" t="n">
         <v>-0.6661</v>
@@ -6065,7 +6065,7 @@
         <v>-0.6409</v>
       </c>
       <c r="C123" t="n">
-        <v>-0</v>
+        <v>-0.4855</v>
       </c>
       <c r="D123" t="n">
         <v>-0.6803</v>
@@ -6111,7 +6111,7 @@
         <v>-0.6566</v>
       </c>
       <c r="C124" t="n">
-        <v>-0</v>
+        <v>-0.4974</v>
       </c>
       <c r="D124" t="n">
         <v>-0.6866</v>
@@ -6157,7 +6157,7 @@
         <v>-0.6568000000000001</v>
       </c>
       <c r="C125" t="n">
-        <v>-0</v>
+        <v>-0.4975</v>
       </c>
       <c r="D125" t="n">
         <v>-0.6867</v>
@@ -6203,7 +6203,7 @@
         <v>-0.6577</v>
       </c>
       <c r="C126" t="n">
-        <v>-0</v>
+        <v>-0.4982</v>
       </c>
       <c r="D126" t="n">
         <v>-0.6871</v>
@@ -6249,7 +6249,7 @@
         <v>-0.7171999999999999</v>
       </c>
       <c r="C127" t="n">
-        <v>-0</v>
+        <v>-0.5433</v>
       </c>
       <c r="D127" t="n">
         <v>-0.7111</v>
@@ -6295,7 +6295,7 @@
         <v>-0.7973</v>
       </c>
       <c r="C128" t="n">
-        <v>-0</v>
+        <v>-0.604</v>
       </c>
       <c r="D128" t="n">
         <v>-0.7435</v>
@@ -6341,7 +6341,7 @@
         <v>-0.8678</v>
       </c>
       <c r="C129" t="n">
-        <v>-0</v>
+        <v>-0.6574</v>
       </c>
       <c r="D129" t="n">
         <v>-0.7719</v>
@@ -6387,7 +6387,7 @@
         <v>-0.8853</v>
       </c>
       <c r="C130" t="n">
-        <v>-0</v>
+        <v>-0.6706</v>
       </c>
       <c r="D130" t="n">
         <v>-0.779</v>
@@ -6433,7 +6433,7 @@
         <v>-0.9001</v>
       </c>
       <c r="C131" t="n">
-        <v>-0</v>
+        <v>-0.6819</v>
       </c>
       <c r="D131" t="n">
         <v>-0.785</v>
@@ -6479,7 +6479,7 @@
         <v>-0.9207</v>
       </c>
       <c r="C132" t="n">
-        <v>-0</v>
+        <v>-0.6975</v>
       </c>
       <c r="D132" t="n">
         <v>-0.7933</v>
@@ -6525,7 +6525,7 @@
         <v>-0.9314</v>
       </c>
       <c r="C133" t="n">
-        <v>-0</v>
+        <v>-0.7056</v>
       </c>
       <c r="D133" t="n">
         <v>-0.7976</v>
@@ -6571,7 +6571,7 @@
         <v>-0.9522</v>
       </c>
       <c r="C134" t="n">
-        <v>-0</v>
+        <v>-0.7213000000000001</v>
       </c>
       <c r="D134" t="n">
         <v>-0.806</v>
@@ -6617,7 +6617,7 @@
         <v>-0.9843</v>
       </c>
       <c r="C135" t="n">
-        <v>-0</v>
+        <v>-0.7456</v>
       </c>
       <c r="D135" t="n">
         <v>-0.819</v>
@@ -6663,7 +6663,7 @@
         <v>-1.0207</v>
       </c>
       <c r="C136" t="n">
-        <v>-0</v>
+        <v>-0.7732</v>
       </c>
       <c r="D136" t="n">
         <v>-0.8337</v>
@@ -6709,7 +6709,7 @@
         <v>-1.0211</v>
       </c>
       <c r="C137" t="n">
-        <v>-0</v>
+        <v>-0.7735</v>
       </c>
       <c r="D137" t="n">
         <v>-0.8339</v>
@@ -6755,7 +6755,7 @@
         <v>-1.1706</v>
       </c>
       <c r="C138" t="n">
-        <v>-0</v>
+        <v>-0.8868</v>
       </c>
       <c r="D138" t="n">
         <v>-0.8943</v>
@@ -6801,7 +6801,7 @@
         <v>-1.1766</v>
       </c>
       <c r="C139" t="n">
-        <v>-0</v>
+        <v>-0.8913</v>
       </c>
       <c r="D139" t="n">
         <v>-0.8967000000000001</v>
@@ -6847,7 +6847,7 @@
         <v>-1.3239</v>
       </c>
       <c r="C140" t="n">
-        <v>-0</v>
+        <v>-1.0029</v>
       </c>
       <c r="D140" t="n">
         <v>-0.9562</v>
@@ -6893,7 +6893,7 @@
         <v>-1.4354</v>
       </c>
       <c r="C141" t="n">
-        <v>-0</v>
+        <v>-1.0874</v>
       </c>
       <c r="D141" t="n">
         <v>-1.0012</v>
@@ -6939,7 +6939,7 @@
         <v>-1.4434</v>
       </c>
       <c r="C142" t="n">
-        <v>-0</v>
+        <v>-1.0934</v>
       </c>
       <c r="D142" t="n">
         <v>-1.0045</v>
@@ -6985,7 +6985,7 @@
         <v>-1.5398</v>
       </c>
       <c r="C143" t="n">
-        <v>-0</v>
+        <v>-1.1665</v>
       </c>
       <c r="D143" t="n">
         <v>-1.0434</v>
@@ -7031,7 +7031,7 @@
         <v>-1.5618</v>
       </c>
       <c r="C144" t="n">
-        <v>-0</v>
+        <v>-1.1831</v>
       </c>
       <c r="D144" t="n">
         <v>-1.0523</v>
@@ -7077,7 +7077,7 @@
         <v>-1.5704</v>
       </c>
       <c r="C145" t="n">
-        <v>-0</v>
+        <v>-1.1896</v>
       </c>
       <c r="D145" t="n">
         <v>-1.0558</v>
@@ -7123,7 +7123,7 @@
         <v>-1.5718</v>
       </c>
       <c r="C146" t="n">
-        <v>-0</v>
+        <v>-1.1907</v>
       </c>
       <c r="D146" t="n">
         <v>-1.0563</v>
@@ -7169,7 +7169,7 @@
         <v>-1.5937</v>
       </c>
       <c r="C147" t="n">
-        <v>-0</v>
+        <v>-1.2073</v>
       </c>
       <c r="D147" t="n">
         <v>-1.0652</v>
@@ -7215,7 +7215,7 @@
         <v>-1.6942</v>
       </c>
       <c r="C148" t="n">
-        <v>-0</v>
+        <v>-1.2834</v>
       </c>
       <c r="D148" t="n">
         <v>-1.1058</v>
@@ -7261,7 +7261,7 @@
         <v>-1.7227</v>
       </c>
       <c r="C149" t="n">
-        <v>-0</v>
+        <v>-1.305</v>
       </c>
       <c r="D149" t="n">
         <v>-1.1173</v>
@@ -7307,7 +7307,7 @@
         <v>-1.8197</v>
       </c>
       <c r="C150" t="n">
-        <v>-0</v>
+        <v>-1.3785</v>
       </c>
       <c r="D150" t="n">
         <v>-1.1565</v>
@@ -7353,7 +7353,7 @@
         <v>-1.8222</v>
       </c>
       <c r="C151" t="n">
-        <v>-0</v>
+        <v>-1.3804</v>
       </c>
       <c r="D151" t="n">
         <v>-1.1575</v>
@@ -7399,7 +7399,7 @@
         <v>-1.9762</v>
       </c>
       <c r="C152" t="n">
-        <v>-0</v>
+        <v>-1.497</v>
       </c>
       <c r="D152" t="n">
         <v>-1.2197</v>
@@ -7445,7 +7445,7 @@
         <v>-2.0044</v>
       </c>
       <c r="C153" t="n">
-        <v>-0</v>
+        <v>-1.5184</v>
       </c>
       <c r="D153" t="n">
         <v>-1.2311</v>
@@ -7491,7 +7491,7 @@
         <v>-2.2921</v>
       </c>
       <c r="C154" t="n">
-        <v>-0</v>
+        <v>-1.7363</v>
       </c>
       <c r="D154" t="n">
         <v>-1.3473</v>
@@ -7537,7 +7537,7 @@
         <v>-2.7012</v>
       </c>
       <c r="C155" t="n">
-        <v>-0</v>
+        <v>-2.0463</v>
       </c>
       <c r="D155" t="n">
         <v>-1.5126</v>
@@ -7583,7 +7583,7 @@
         <v>-2.7412</v>
       </c>
       <c r="C156" t="n">
-        <v>-0</v>
+        <v>-2.0766</v>
       </c>
       <c r="D156" t="n">
         <v>-1.5287</v>
@@ -7629,7 +7629,7 @@
         <v>-2.9266</v>
       </c>
       <c r="C157" t="n">
-        <v>-0</v>
+        <v>-2.217</v>
       </c>
       <c r="D157" t="n">
         <v>-1.6036</v>
@@ -7675,7 +7675,7 @@
         <v>-2.9325</v>
       </c>
       <c r="C158" t="n">
-        <v>-0</v>
+        <v>-2.2215</v>
       </c>
       <c r="D158" t="n">
         <v>-1.606</v>
@@ -7721,7 +7721,7 @@
         <v>-2.9827</v>
       </c>
       <c r="C159" t="n">
-        <v>-0</v>
+        <v>-2.2595</v>
       </c>
       <c r="D159" t="n">
         <v>-1.6263</v>
@@ -7767,7 +7767,7 @@
         <v>-4.491</v>
       </c>
       <c r="C160" t="n">
-        <v>-0</v>
+        <v>-3.4021</v>
       </c>
       <c r="D160" t="n">
         <v>-2.2356</v>
@@ -7813,7 +7813,7 @@
         <v>-5.0728</v>
       </c>
       <c r="C161" t="n">
-        <v>-0</v>
+        <v>-3.8428</v>
       </c>
       <c r="D161" t="n">
         <v>-2.4707</v>

--- a/database/event/6863/event_6863_evp_summary.xlsx
+++ b/database/event/6863/event_6863_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.8434</v>
+        <v>10.782</v>
       </c>
       <c r="C2" t="n">
-        <v>8.2142</v>
+        <v>8.1677</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9591</v>
+        <v>3.8516</v>
       </c>
       <c r="E2" t="n">
-        <v>10.8434</v>
+        <v>10.782</v>
       </c>
       <c r="F2" t="n">
-        <v>4.7861</v>
+        <v>4.7247</v>
       </c>
       <c r="G2" t="n">
         <v>6.0573</v>
       </c>
       <c r="H2" t="n">
-        <v>5.2016</v>
+        <v>5.1053</v>
       </c>
       <c r="I2" t="n">
         <v>5.3238</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10.6404</v>
+        <v>10.5492</v>
       </c>
       <c r="C3" t="n">
-        <v>8.060499999999999</v>
+        <v>7.9914</v>
       </c>
       <c r="D3" t="n">
-        <v>3.8771</v>
+        <v>3.7589</v>
       </c>
       <c r="E3" t="n">
-        <v>10.6404</v>
+        <v>10.5492</v>
       </c>
       <c r="F3" t="n">
-        <v>6.3982</v>
+        <v>6.3069</v>
       </c>
       <c r="G3" t="n">
         <v>4.2422</v>
       </c>
       <c r="H3" t="n">
-        <v>7.7293</v>
+        <v>7.5862</v>
       </c>
       <c r="I3" t="n">
         <v>7.9108</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.968</v>
+        <v>8.9129</v>
       </c>
       <c r="C4" t="n">
-        <v>6.7936</v>
+        <v>6.7518</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2015</v>
+        <v>3.107</v>
       </c>
       <c r="E4" t="n">
-        <v>8.968</v>
+        <v>8.9129</v>
       </c>
       <c r="F4" t="n">
-        <v>4.4492</v>
+        <v>4.3941</v>
       </c>
       <c r="G4" t="n">
         <v>4.5188</v>
       </c>
       <c r="H4" t="n">
-        <v>4.6734</v>
+        <v>4.5868</v>
       </c>
       <c r="I4" t="n">
         <v>4.7831</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.8089</v>
+        <v>7.7471</v>
       </c>
       <c r="C5" t="n">
-        <v>5.9155</v>
+        <v>5.8687</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7333</v>
+        <v>2.6425</v>
       </c>
       <c r="E5" t="n">
-        <v>7.8089</v>
+        <v>7.7471</v>
       </c>
       <c r="F5" t="n">
-        <v>4.806</v>
+        <v>4.7442</v>
       </c>
       <c r="G5" t="n">
         <v>3.0029</v>
       </c>
       <c r="H5" t="n">
-        <v>5.2327</v>
+        <v>5.1358</v>
       </c>
       <c r="I5" t="n">
         <v>5.3556</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.5286</v>
+        <v>7.4385</v>
       </c>
       <c r="C6" t="n">
-        <v>5.7032</v>
+        <v>5.6349</v>
       </c>
       <c r="D6" t="n">
-        <v>2.62</v>
+        <v>2.5196</v>
       </c>
       <c r="E6" t="n">
-        <v>7.5286</v>
+        <v>7.4385</v>
       </c>
       <c r="F6" t="n">
-        <v>5.5323</v>
+        <v>5.4422</v>
       </c>
       <c r="G6" t="n">
         <v>1.9962</v>
       </c>
       <c r="H6" t="n">
-        <v>6.3716</v>
+        <v>6.2303</v>
       </c>
       <c r="I6" t="n">
         <v>6.5516</v>
@@ -732,7 +732,7 @@
         <v>5.3399</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4263</v>
+        <v>2.3644</v>
       </c>
       <c r="E7" t="n">
         <v>7.049</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.381</v>
+        <v>6.3261</v>
       </c>
       <c r="C8" t="n">
-        <v>4.8338</v>
+        <v>4.7922</v>
       </c>
       <c r="D8" t="n">
-        <v>2.1564</v>
+        <v>2.0764</v>
       </c>
       <c r="E8" t="n">
-        <v>6.381</v>
+        <v>6.3261</v>
       </c>
       <c r="F8" t="n">
-        <v>6.4635</v>
+        <v>6.4086</v>
       </c>
       <c r="G8" t="n">
         <v>-0.0825</v>
       </c>
       <c r="H8" t="n">
-        <v>7.8623</v>
+        <v>7.7456</v>
       </c>
       <c r="I8" t="n">
         <v>8.0097</v>
@@ -824,7 +824,7 @@
         <v>4.6522</v>
       </c>
       <c r="D9" t="n">
-        <v>2.0596</v>
+        <v>2.0028</v>
       </c>
       <c r="E9" t="n">
         <v>6.1413</v>
@@ -870,7 +870,7 @@
         <v>4.6226</v>
       </c>
       <c r="D10" t="n">
-        <v>2.0438</v>
+        <v>1.9872</v>
       </c>
       <c r="E10" t="n">
         <v>6.1022</v>
@@ -916,7 +916,7 @@
         <v>4.1596</v>
       </c>
       <c r="D11" t="n">
-        <v>1.7969</v>
+        <v>1.7437</v>
       </c>
       <c r="E11" t="n">
         <v>5.491</v>
@@ -962,7 +962,7 @@
         <v>4.0549</v>
       </c>
       <c r="D12" t="n">
-        <v>1.7411</v>
+        <v>1.6886</v>
       </c>
       <c r="E12" t="n">
         <v>5.3528</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.2736</v>
+        <v>5.2051</v>
       </c>
       <c r="C13" t="n">
-        <v>3.9949</v>
+        <v>3.943</v>
       </c>
       <c r="D13" t="n">
-        <v>1.7091</v>
+        <v>1.6298</v>
       </c>
       <c r="E13" t="n">
-        <v>5.2736</v>
+        <v>5.2051</v>
       </c>
       <c r="F13" t="n">
-        <v>4.5565</v>
+        <v>4.488</v>
       </c>
       <c r="G13" t="n">
         <v>0.7171</v>
       </c>
       <c r="H13" t="n">
-        <v>4.8415</v>
+        <v>4.7341</v>
       </c>
       <c r="I13" t="n">
         <v>4.9783</v>
@@ -1044,93 +1044,93 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>ZywOo</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.2071</v>
+        <v>5.1974</v>
       </c>
       <c r="C14" t="n">
-        <v>3.9446</v>
+        <v>3.9372</v>
       </c>
       <c r="D14" t="n">
-        <v>1.6822</v>
+        <v>1.6267</v>
       </c>
       <c r="E14" t="n">
-        <v>5.2071</v>
+        <v>5.1974</v>
       </c>
       <c r="F14" t="n">
-        <v>5.2071</v>
+        <v>4.6295</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.5679</v>
       </c>
       <c r="H14" t="n">
-        <v>5.8617</v>
+        <v>4.9559</v>
       </c>
       <c r="I14" t="n">
-        <v>5.9164</v>
+        <v>4.9559</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>0.5679</v>
       </c>
       <c r="K14" t="n">
-        <v>362</v>
+        <v>138</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="M14" t="n">
-        <v>5.9164</v>
+        <v>5.5238</v>
       </c>
       <c r="N14" t="n">
-        <v>362</v>
+        <v>195</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ZywOo</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.1974</v>
+        <v>5.1793</v>
       </c>
       <c r="C15" t="n">
-        <v>3.9372</v>
+        <v>3.9235</v>
       </c>
       <c r="D15" t="n">
-        <v>1.6783</v>
+        <v>1.6195</v>
       </c>
       <c r="E15" t="n">
-        <v>5.1974</v>
+        <v>5.1793</v>
       </c>
       <c r="F15" t="n">
-        <v>4.6295</v>
+        <v>5.1793</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5679</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>4.9559</v>
+        <v>5.8181</v>
       </c>
       <c r="I15" t="n">
-        <v>4.9559</v>
+        <v>5.9164</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5679</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>138</v>
+        <v>362</v>
       </c>
       <c r="L15" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>5.5238</v>
+        <v>5.9164</v>
       </c>
       <c r="N15" t="n">
-        <v>195</v>
+        <v>362</v>
       </c>
     </row>
     <row r="16">
@@ -1146,7 +1146,7 @@
         <v>3.7313</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5685</v>
+        <v>1.5184</v>
       </c>
       <c r="E16" t="n">
         <v>4.9256</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4.9184</v>
+        <v>4.8412</v>
       </c>
       <c r="C17" t="n">
-        <v>3.7259</v>
+        <v>3.6674</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5656</v>
+        <v>1.4848</v>
       </c>
       <c r="E17" t="n">
-        <v>4.9184</v>
+        <v>4.8412</v>
       </c>
       <c r="F17" t="n">
-        <v>4.9465</v>
+        <v>4.8693</v>
       </c>
       <c r="G17" t="n">
         <v>-0.0281</v>
       </c>
       <c r="H17" t="n">
-        <v>5.453</v>
+        <v>5.3321</v>
       </c>
       <c r="I17" t="n">
         <v>5.607</v>
@@ -1232,25 +1232,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4.8429</v>
+        <v>4.8178</v>
       </c>
       <c r="C18" t="n">
-        <v>3.6687</v>
+        <v>3.6496</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5351</v>
+        <v>1.4755</v>
       </c>
       <c r="E18" t="n">
-        <v>4.8429</v>
+        <v>4.8178</v>
       </c>
       <c r="F18" t="n">
-        <v>4.8429</v>
+        <v>4.8178</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>5.2906</v>
+        <v>5.2512</v>
       </c>
       <c r="I18" t="n">
         <v>5.34</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.2995</v>
+        <v>4.2889</v>
       </c>
       <c r="C19" t="n">
-        <v>3.257</v>
+        <v>3.249</v>
       </c>
       <c r="D19" t="n">
-        <v>1.3155</v>
+        <v>1.2648</v>
       </c>
       <c r="E19" t="n">
-        <v>4.2995</v>
+        <v>4.2889</v>
       </c>
       <c r="F19" t="n">
-        <v>4.2995</v>
+        <v>4.2889</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>4.4386</v>
+        <v>4.422</v>
       </c>
       <c r="I19" t="n">
         <v>4.4592</v>
@@ -1330,7 +1330,7 @@
         <v>3.1441</v>
       </c>
       <c r="D20" t="n">
-        <v>1.2553</v>
+        <v>1.2096</v>
       </c>
       <c r="E20" t="n">
         <v>4.1505</v>
@@ -1376,7 +1376,7 @@
         <v>3.115</v>
       </c>
       <c r="D21" t="n">
-        <v>1.2398</v>
+        <v>1.1943</v>
       </c>
       <c r="E21" t="n">
         <v>4.112</v>
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4.0728</v>
+        <v>4.0376</v>
       </c>
       <c r="C22" t="n">
-        <v>3.0853</v>
+        <v>3.0586</v>
       </c>
       <c r="D22" t="n">
-        <v>1.224</v>
+        <v>1.1647</v>
       </c>
       <c r="E22" t="n">
-        <v>4.0728</v>
+        <v>4.0376</v>
       </c>
       <c r="F22" t="n">
-        <v>4.0728</v>
+        <v>4.0376</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>4.0831</v>
+        <v>4.0376</v>
       </c>
       <c r="I22" t="n">
         <v>4.1404</v>
@@ -1458,93 +1458,93 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3.9284</v>
+        <v>3.9089</v>
       </c>
       <c r="C23" t="n">
-        <v>2.9759</v>
+        <v>2.9611</v>
       </c>
       <c r="D23" t="n">
-        <v>1.1656</v>
+        <v>1.1134</v>
       </c>
       <c r="E23" t="n">
-        <v>3.9284</v>
+        <v>3.9089</v>
       </c>
       <c r="F23" t="n">
-        <v>3.9284</v>
+        <v>2.9713</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>0.9376</v>
       </c>
       <c r="H23" t="n">
-        <v>3.9284</v>
+        <v>2.9713</v>
       </c>
       <c r="I23" t="n">
-        <v>3.9651</v>
+        <v>2.9713</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>0.9376</v>
       </c>
       <c r="K23" t="n">
-        <v>377</v>
+        <v>138</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="M23" t="n">
-        <v>3.9651</v>
+        <v>3.9089</v>
       </c>
       <c r="N23" t="n">
-        <v>377</v>
+        <v>195</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.9089</v>
+        <v>3.8992</v>
       </c>
       <c r="C24" t="n">
-        <v>2.9611</v>
+        <v>2.9538</v>
       </c>
       <c r="D24" t="n">
-        <v>1.1577</v>
+        <v>1.1095</v>
       </c>
       <c r="E24" t="n">
-        <v>3.9089</v>
+        <v>3.8992</v>
       </c>
       <c r="F24" t="n">
-        <v>2.9713</v>
+        <v>3.8992</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9376</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2.9713</v>
+        <v>3.8992</v>
       </c>
       <c r="I24" t="n">
-        <v>2.9713</v>
+        <v>3.9651</v>
       </c>
       <c r="J24" t="n">
-        <v>0.9376</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>138</v>
+        <v>377</v>
       </c>
       <c r="L24" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.9089</v>
+        <v>3.9651</v>
       </c>
       <c r="N24" t="n">
-        <v>195</v>
+        <v>377</v>
       </c>
     </row>
     <row r="25">
@@ -1554,25 +1554,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3.6819</v>
+        <v>3.6389</v>
       </c>
       <c r="C25" t="n">
-        <v>2.7892</v>
+        <v>2.7566</v>
       </c>
       <c r="D25" t="n">
-        <v>1.066</v>
+        <v>1.0058</v>
       </c>
       <c r="E25" t="n">
-        <v>3.6819</v>
+        <v>3.6389</v>
       </c>
       <c r="F25" t="n">
-        <v>4.3632</v>
+        <v>4.3202</v>
       </c>
       <c r="G25" t="n">
         <v>-0.6813</v>
       </c>
       <c r="H25" t="n">
-        <v>4.5384</v>
+        <v>4.471</v>
       </c>
       <c r="I25" t="n">
         <v>4.6235</v>
@@ -1606,7 +1606,7 @@
         <v>2.5308</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9282</v>
+        <v>0.8871</v>
       </c>
       <c r="E26" t="n">
         <v>3.3408</v>
@@ -1652,7 +1652,7 @@
         <v>2.5118</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9181</v>
+        <v>0.8771</v>
       </c>
       <c r="E27" t="n">
         <v>3.3158</v>
@@ -1698,7 +1698,7 @@
         <v>2.5051</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9146</v>
+        <v>0.8736</v>
       </c>
       <c r="E28" t="n">
         <v>3.3069</v>
@@ -1744,7 +1744,7 @@
         <v>2.4232</v>
       </c>
       <c r="D29" t="n">
-        <v>0.8709</v>
+        <v>0.8305</v>
       </c>
       <c r="E29" t="n">
         <v>3.1988</v>
@@ -1780,93 +1780,93 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>insani</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3.1888</v>
+        <v>3.138</v>
       </c>
       <c r="C30" t="n">
-        <v>2.4156</v>
+        <v>2.3771</v>
       </c>
       <c r="D30" t="n">
-        <v>0.8668</v>
+        <v>0.8063</v>
       </c>
       <c r="E30" t="n">
-        <v>3.1888</v>
+        <v>3.138</v>
       </c>
       <c r="F30" t="n">
-        <v>3.3849</v>
+        <v>3.138</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.1961</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>3.3849</v>
+        <v>3.138</v>
       </c>
       <c r="I30" t="n">
-        <v>3.4644</v>
+        <v>3.1644</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.1961</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>330</v>
+        <v>456</v>
       </c>
       <c r="L30" t="n">
-        <v>247</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.2683</v>
+        <v>3.1644</v>
       </c>
       <c r="N30" t="n">
-        <v>577</v>
+        <v>456</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>insani</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3.1497</v>
+        <v>3.1261</v>
       </c>
       <c r="C31" t="n">
-        <v>2.386</v>
+        <v>2.3681</v>
       </c>
       <c r="D31" t="n">
-        <v>0.851</v>
+        <v>0.8015</v>
       </c>
       <c r="E31" t="n">
-        <v>3.1497</v>
+        <v>3.1261</v>
       </c>
       <c r="F31" t="n">
-        <v>3.1497</v>
+        <v>3.3222</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>-0.1961</v>
       </c>
       <c r="H31" t="n">
-        <v>3.1497</v>
+        <v>3.3222</v>
       </c>
       <c r="I31" t="n">
-        <v>3.1644</v>
+        <v>3.4644</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>-0.1961</v>
       </c>
       <c r="K31" t="n">
-        <v>456</v>
+        <v>330</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>247</v>
       </c>
       <c r="M31" t="n">
-        <v>3.1644</v>
+        <v>3.2683</v>
       </c>
       <c r="N31" t="n">
-        <v>456</v>
+        <v>577</v>
       </c>
     </row>
     <row r="32">
@@ -1882,7 +1882,7 @@
         <v>2.3671</v>
       </c>
       <c r="D32" t="n">
-        <v>0.841</v>
+        <v>0.801</v>
       </c>
       <c r="E32" t="n">
         <v>3.1248</v>
@@ -1928,7 +1928,7 @@
         <v>2.2943</v>
       </c>
       <c r="D33" t="n">
-        <v>0.8022</v>
+        <v>0.7627</v>
       </c>
       <c r="E33" t="n">
         <v>3.0287</v>
@@ -1968,25 +1968,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.8797</v>
+        <v>2.8476</v>
       </c>
       <c r="C34" t="n">
-        <v>2.1815</v>
+        <v>2.1572</v>
       </c>
       <c r="D34" t="n">
-        <v>0.742</v>
+        <v>0.6906</v>
       </c>
       <c r="E34" t="n">
-        <v>2.8797</v>
+        <v>2.8476</v>
       </c>
       <c r="F34" t="n">
-        <v>2.8797</v>
+        <v>2.8476</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>2.8797</v>
+        <v>2.8476</v>
       </c>
       <c r="I34" t="n">
         <v>2.9201</v>
@@ -2020,7 +2020,7 @@
         <v>2.1516</v>
       </c>
       <c r="D35" t="n">
-        <v>0.7261</v>
+        <v>0.6877</v>
       </c>
       <c r="E35" t="n">
         <v>2.8403</v>
@@ -2066,7 +2066,7 @@
         <v>2.1121</v>
       </c>
       <c r="D36" t="n">
-        <v>0.705</v>
+        <v>0.6669</v>
       </c>
       <c r="E36" t="n">
         <v>2.7881</v>
@@ -2112,7 +2112,7 @@
         <v>2.0577</v>
       </c>
       <c r="D37" t="n">
-        <v>0.676</v>
+        <v>0.6383</v>
       </c>
       <c r="E37" t="n">
         <v>2.7163</v>
@@ -2158,7 +2158,7 @@
         <v>2.0563</v>
       </c>
       <c r="D38" t="n">
-        <v>0.6752</v>
+        <v>0.6375</v>
       </c>
       <c r="E38" t="n">
         <v>2.7144</v>
@@ -2204,7 +2204,7 @@
         <v>2.0391</v>
       </c>
       <c r="D39" t="n">
-        <v>0.666</v>
+        <v>0.6284999999999999</v>
       </c>
       <c r="E39" t="n">
         <v>2.6917</v>
@@ -2244,25 +2244,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2.6484</v>
+        <v>2.6287</v>
       </c>
       <c r="C40" t="n">
-        <v>2.0063</v>
+        <v>1.9913</v>
       </c>
       <c r="D40" t="n">
-        <v>0.6485</v>
+        <v>0.6034</v>
       </c>
       <c r="E40" t="n">
-        <v>2.6484</v>
+        <v>2.6287</v>
       </c>
       <c r="F40" t="n">
-        <v>2.6484</v>
+        <v>2.6287</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>2.6484</v>
+        <v>2.6287</v>
       </c>
       <c r="I40" t="n">
         <v>2.6731</v>
@@ -2286,185 +2286,185 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>arT</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2.5587</v>
+        <v>2.5429</v>
       </c>
       <c r="C41" t="n">
-        <v>1.9383</v>
+        <v>1.9263</v>
       </c>
       <c r="D41" t="n">
-        <v>0.6123</v>
+        <v>0.5692</v>
       </c>
       <c r="E41" t="n">
-        <v>2.5587</v>
+        <v>2.5429</v>
       </c>
       <c r="F41" t="n">
-        <v>2.5587</v>
+        <v>2.5429</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>2.5587</v>
+        <v>2.5429</v>
       </c>
       <c r="I41" t="n">
-        <v>2.5826</v>
+        <v>2.5429</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>362</v>
+        <v>286</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>2.5826</v>
+        <v>2.5429</v>
       </c>
       <c r="N41" t="n">
-        <v>362</v>
+        <v>286</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>arT</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2.5429</v>
+        <v>2.5397</v>
       </c>
       <c r="C42" t="n">
-        <v>1.9263</v>
+        <v>1.9239</v>
       </c>
       <c r="D42" t="n">
-        <v>0.6059</v>
+        <v>0.5679</v>
       </c>
       <c r="E42" t="n">
-        <v>2.5429</v>
+        <v>2.5397</v>
       </c>
       <c r="F42" t="n">
-        <v>2.5429</v>
+        <v>2.5397</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>2.5429</v>
+        <v>2.5397</v>
       </c>
       <c r="I42" t="n">
-        <v>2.5429</v>
+        <v>2.5826</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>286</v>
+        <v>362</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>2.5429</v>
+        <v>2.5826</v>
       </c>
       <c r="N42" t="n">
-        <v>286</v>
+        <v>362</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>dav1deuS</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2.468</v>
+        <v>2.4498</v>
       </c>
       <c r="C43" t="n">
-        <v>1.8696</v>
+        <v>1.8558</v>
       </c>
       <c r="D43" t="n">
-        <v>0.5757</v>
+        <v>0.5321</v>
       </c>
       <c r="E43" t="n">
-        <v>2.468</v>
+        <v>2.4498</v>
       </c>
       <c r="F43" t="n">
-        <v>2.468</v>
+        <v>2.6368</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>-0.187</v>
       </c>
       <c r="H43" t="n">
-        <v>2.468</v>
+        <v>2.6368</v>
       </c>
       <c r="I43" t="n">
-        <v>2.5026</v>
+        <v>2.6368</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>-0.187</v>
       </c>
       <c r="K43" t="n">
-        <v>446</v>
+        <v>204</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="M43" t="n">
-        <v>2.5026</v>
+        <v>2.4498</v>
       </c>
       <c r="N43" t="n">
-        <v>446</v>
+        <v>286</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>dav1deuS</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2.4498</v>
+        <v>2.4405</v>
       </c>
       <c r="C44" t="n">
-        <v>1.8558</v>
+        <v>1.8488</v>
       </c>
       <c r="D44" t="n">
-        <v>0.5683</v>
+        <v>0.5284</v>
       </c>
       <c r="E44" t="n">
-        <v>2.4498</v>
+        <v>2.4405</v>
       </c>
       <c r="F44" t="n">
-        <v>2.6368</v>
+        <v>2.4405</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.187</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>2.6368</v>
+        <v>2.4405</v>
       </c>
       <c r="I44" t="n">
-        <v>2.6368</v>
+        <v>2.5026</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.187</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>204</v>
+        <v>446</v>
       </c>
       <c r="L44" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>2.4498</v>
+        <v>2.5026</v>
       </c>
       <c r="N44" t="n">
-        <v>286</v>
+        <v>446</v>
       </c>
     </row>
     <row r="45">
@@ -2480,7 +2480,7 @@
         <v>1.8246</v>
       </c>
       <c r="D45" t="n">
-        <v>0.5517</v>
+        <v>0.5157</v>
       </c>
       <c r="E45" t="n">
         <v>2.4086</v>
@@ -2526,7 +2526,7 @@
         <v>1.7276</v>
       </c>
       <c r="D46" t="n">
-        <v>0.4999</v>
+        <v>0.4647</v>
       </c>
       <c r="E46" t="n">
         <v>2.2806</v>
@@ -2566,25 +2566,25 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2.2747</v>
+        <v>2.2577</v>
       </c>
       <c r="C47" t="n">
-        <v>1.7232</v>
+        <v>1.7103</v>
       </c>
       <c r="D47" t="n">
-        <v>0.4976</v>
+        <v>0.4556</v>
       </c>
       <c r="E47" t="n">
-        <v>2.2747</v>
+        <v>2.2577</v>
       </c>
       <c r="F47" t="n">
-        <v>2.2747</v>
+        <v>2.2577</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>2.2747</v>
+        <v>2.2577</v>
       </c>
       <c r="I47" t="n">
         <v>2.2959</v>
@@ -2608,53 +2608,53 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>afro</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2.2532</v>
+        <v>2.2364</v>
       </c>
       <c r="C48" t="n">
-        <v>1.7069</v>
+        <v>1.6941</v>
       </c>
       <c r="D48" t="n">
-        <v>0.4889</v>
+        <v>0.4471</v>
       </c>
       <c r="E48" t="n">
-        <v>2.2532</v>
+        <v>2.2364</v>
       </c>
       <c r="F48" t="n">
-        <v>2.2532</v>
+        <v>2.2364</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>2.2532</v>
+        <v>2.2364</v>
       </c>
       <c r="I48" t="n">
-        <v>2.2742</v>
+        <v>2.2364</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>377</v>
+        <v>310</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>2.2742</v>
+        <v>2.2364</v>
       </c>
       <c r="N48" t="n">
-        <v>377</v>
+        <v>310</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>afro</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2664,7 +2664,7 @@
         <v>1.6941</v>
       </c>
       <c r="D49" t="n">
-        <v>0.4821</v>
+        <v>0.4471</v>
       </c>
       <c r="E49" t="n">
         <v>2.2364</v>
@@ -2679,22 +2679,22 @@
         <v>2.2364</v>
       </c>
       <c r="I49" t="n">
-        <v>2.2364</v>
+        <v>2.2742</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>310</v>
+        <v>377</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>2.2364</v>
+        <v>2.2742</v>
       </c>
       <c r="N49" t="n">
-        <v>310</v>
+        <v>377</v>
       </c>
     </row>
     <row r="50">
@@ -2704,25 +2704,25 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2.1779</v>
+        <v>2.1617</v>
       </c>
       <c r="C50" t="n">
-        <v>1.6498</v>
+        <v>1.6376</v>
       </c>
       <c r="D50" t="n">
-        <v>0.4585</v>
+        <v>0.4173</v>
       </c>
       <c r="E50" t="n">
-        <v>2.1779</v>
+        <v>2.1617</v>
       </c>
       <c r="F50" t="n">
-        <v>2.1779</v>
+        <v>2.1617</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>2.1779</v>
+        <v>2.1617</v>
       </c>
       <c r="I50" t="n">
         <v>2.1982</v>
@@ -2756,7 +2756,7 @@
         <v>1.602</v>
       </c>
       <c r="D51" t="n">
-        <v>0.433</v>
+        <v>0.3986</v>
       </c>
       <c r="E51" t="n">
         <v>2.1148</v>
@@ -2802,7 +2802,7 @@
         <v>1.5658</v>
       </c>
       <c r="D52" t="n">
-        <v>0.4137</v>
+        <v>0.3796</v>
       </c>
       <c r="E52" t="n">
         <v>2.067</v>
@@ -2838,93 +2838,93 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>mir</t>
+          <t>prosus</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1.8613</v>
+        <v>1.856</v>
       </c>
       <c r="C53" t="n">
-        <v>1.41</v>
+        <v>1.406</v>
       </c>
       <c r="D53" t="n">
-        <v>0.3306</v>
+        <v>0.2955</v>
       </c>
       <c r="E53" t="n">
-        <v>1.8613</v>
+        <v>1.856</v>
       </c>
       <c r="F53" t="n">
-        <v>1.8613</v>
+        <v>1.856</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>1.8613</v>
+        <v>1.856</v>
       </c>
       <c r="I53" t="n">
-        <v>1.8787</v>
+        <v>1.856</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>382</v>
+        <v>295</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>1.8787</v>
+        <v>1.856</v>
       </c>
       <c r="N53" t="n">
-        <v>382</v>
+        <v>295</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>prosus</t>
+          <t>mir</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1.856</v>
+        <v>1.8475</v>
       </c>
       <c r="C54" t="n">
-        <v>1.406</v>
+        <v>1.3995</v>
       </c>
       <c r="D54" t="n">
-        <v>0.3284</v>
+        <v>0.2921</v>
       </c>
       <c r="E54" t="n">
-        <v>1.856</v>
+        <v>1.8475</v>
       </c>
       <c r="F54" t="n">
-        <v>1.856</v>
+        <v>1.8475</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>1.856</v>
+        <v>1.8475</v>
       </c>
       <c r="I54" t="n">
-        <v>1.856</v>
+        <v>1.8787</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>295</v>
+        <v>382</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>1.856</v>
+        <v>1.8787</v>
       </c>
       <c r="N54" t="n">
-        <v>295</v>
+        <v>382</v>
       </c>
     </row>
     <row r="55">
@@ -2940,7 +2940,7 @@
         <v>1.3789</v>
       </c>
       <c r="D55" t="n">
-        <v>0.314</v>
+        <v>0.2813</v>
       </c>
       <c r="E55" t="n">
         <v>1.8202</v>
@@ -2986,7 +2986,7 @@
         <v>1.3735</v>
       </c>
       <c r="D56" t="n">
-        <v>0.3111</v>
+        <v>0.2784</v>
       </c>
       <c r="E56" t="n">
         <v>1.8131</v>
@@ -3022,93 +3022,93 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>max</t>
+          <t>br0</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1.7862</v>
+        <v>1.7826</v>
       </c>
       <c r="C57" t="n">
-        <v>1.3531</v>
+        <v>1.3504</v>
       </c>
       <c r="D57" t="n">
-        <v>0.3002</v>
+        <v>0.2663</v>
       </c>
       <c r="E57" t="n">
-        <v>1.7862</v>
+        <v>1.7826</v>
       </c>
       <c r="F57" t="n">
-        <v>1.7862</v>
+        <v>0.0044</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>1.7782</v>
       </c>
       <c r="H57" t="n">
-        <v>1.7862</v>
+        <v>0.0044</v>
       </c>
       <c r="I57" t="n">
-        <v>1.8113</v>
+        <v>0.0046</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>1.7782</v>
       </c>
       <c r="K57" t="n">
-        <v>446</v>
+        <v>519</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="M57" t="n">
-        <v>1.8113</v>
+        <v>1.7828</v>
       </c>
       <c r="N57" t="n">
-        <v>446</v>
+        <v>630</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>br0</t>
+          <t>max</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1.7827</v>
+        <v>1.7663</v>
       </c>
       <c r="C58" t="n">
-        <v>1.3505</v>
+        <v>1.338</v>
       </c>
       <c r="D58" t="n">
-        <v>0.2988</v>
+        <v>0.2598</v>
       </c>
       <c r="E58" t="n">
-        <v>1.7827</v>
+        <v>1.7663</v>
       </c>
       <c r="F58" t="n">
-        <v>0.0045</v>
+        <v>1.7663</v>
       </c>
       <c r="G58" t="n">
-        <v>1.7782</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0.0045</v>
+        <v>1.7663</v>
       </c>
       <c r="I58" t="n">
-        <v>0.0046</v>
+        <v>1.8113</v>
       </c>
       <c r="J58" t="n">
-        <v>1.7782</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>519</v>
+        <v>446</v>
       </c>
       <c r="L58" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>1.7828</v>
+        <v>1.8113</v>
       </c>
       <c r="N58" t="n">
-        <v>630</v>
+        <v>446</v>
       </c>
     </row>
     <row r="59">
@@ -3124,7 +3124,7 @@
         <v>1.3186</v>
       </c>
       <c r="D59" t="n">
-        <v>0.2818</v>
+        <v>0.2495</v>
       </c>
       <c r="E59" t="n">
         <v>1.7406</v>
@@ -3170,7 +3170,7 @@
         <v>1.264</v>
       </c>
       <c r="D60" t="n">
-        <v>0.2527</v>
+        <v>0.2209</v>
       </c>
       <c r="E60" t="n">
         <v>1.6686</v>
@@ -3210,25 +3210,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1.6279</v>
+        <v>1.6158</v>
       </c>
       <c r="C61" t="n">
-        <v>1.2332</v>
+        <v>1.224</v>
       </c>
       <c r="D61" t="n">
-        <v>0.2363</v>
+        <v>0.1998</v>
       </c>
       <c r="E61" t="n">
-        <v>1.6279</v>
+        <v>1.6158</v>
       </c>
       <c r="F61" t="n">
-        <v>1.6279</v>
+        <v>1.6158</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>1.6279</v>
+        <v>1.6158</v>
       </c>
       <c r="I61" t="n">
         <v>1.6431</v>
@@ -3262,7 +3262,7 @@
         <v>1.2177</v>
       </c>
       <c r="D62" t="n">
-        <v>0.228</v>
+        <v>0.1965</v>
       </c>
       <c r="E62" t="n">
         <v>1.6074</v>
@@ -3308,7 +3308,7 @@
         <v>1.1672</v>
       </c>
       <c r="D63" t="n">
-        <v>0.2011</v>
+        <v>0.1699</v>
       </c>
       <c r="E63" t="n">
         <v>1.5408</v>
@@ -3354,7 +3354,7 @@
         <v>1.1551</v>
       </c>
       <c r="D64" t="n">
-        <v>0.1946</v>
+        <v>0.1636</v>
       </c>
       <c r="E64" t="n">
         <v>1.5248</v>
@@ -3400,7 +3400,7 @@
         <v>1.0778</v>
       </c>
       <c r="D65" t="n">
-        <v>0.1534</v>
+        <v>0.1229</v>
       </c>
       <c r="E65" t="n">
         <v>1.4228</v>
@@ -3440,25 +3440,25 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1.3909</v>
+        <v>1.3596</v>
       </c>
       <c r="C66" t="n">
-        <v>1.0537</v>
+        <v>1.0299</v>
       </c>
       <c r="D66" t="n">
-        <v>0.1405</v>
+        <v>0.0978</v>
       </c>
       <c r="E66" t="n">
-        <v>1.3909</v>
+        <v>1.3596</v>
       </c>
       <c r="F66" t="n">
-        <v>1.4119</v>
+        <v>1.3806</v>
       </c>
       <c r="G66" t="n">
         <v>-0.021</v>
       </c>
       <c r="H66" t="n">
-        <v>1.4119</v>
+        <v>1.3806</v>
       </c>
       <c r="I66" t="n">
         <v>1.4518</v>
@@ -3492,7 +3492,7 @@
         <v>1.0029</v>
       </c>
       <c r="D67" t="n">
-        <v>0.1135</v>
+        <v>0.0835</v>
       </c>
       <c r="E67" t="n">
         <v>1.3239</v>
@@ -3538,7 +3538,7 @@
         <v>1.0023</v>
       </c>
       <c r="D68" t="n">
-        <v>0.1131</v>
+        <v>0.0832</v>
       </c>
       <c r="E68" t="n">
         <v>1.3231</v>
@@ -3578,25 +3578,25 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1.274</v>
+        <v>1.2645</v>
       </c>
       <c r="C69" t="n">
-        <v>0.9651</v>
+        <v>0.9579</v>
       </c>
       <c r="D69" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.0599</v>
       </c>
       <c r="E69" t="n">
-        <v>1.274</v>
+        <v>1.2645</v>
       </c>
       <c r="F69" t="n">
-        <v>1.274</v>
+        <v>1.2645</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>1.274</v>
+        <v>1.2645</v>
       </c>
       <c r="I69" t="n">
         <v>1.2858</v>
@@ -3630,7 +3630,7 @@
         <v>0.9465</v>
       </c>
       <c r="D70" t="n">
-        <v>0.0834</v>
+        <v>0.0539</v>
       </c>
       <c r="E70" t="n">
         <v>1.2494</v>
@@ -3670,25 +3670,25 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1.1672</v>
+        <v>1.1585</v>
       </c>
       <c r="C71" t="n">
-        <v>0.8842</v>
+        <v>0.8776</v>
       </c>
       <c r="D71" t="n">
-        <v>0.0502</v>
+        <v>0.0176</v>
       </c>
       <c r="E71" t="n">
-        <v>1.1672</v>
+        <v>1.1585</v>
       </c>
       <c r="F71" t="n">
-        <v>1.1672</v>
+        <v>1.1585</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>1.1672</v>
+        <v>1.1585</v>
       </c>
       <c r="I71" t="n">
         <v>1.1781</v>
@@ -3722,7 +3722,7 @@
         <v>0.8566</v>
       </c>
       <c r="D72" t="n">
-        <v>0.0355</v>
+        <v>0.0066</v>
       </c>
       <c r="E72" t="n">
         <v>1.1308</v>
@@ -3768,7 +3768,7 @@
         <v>0.8512999999999999</v>
       </c>
       <c r="D73" t="n">
-        <v>0.0326</v>
+        <v>0.0038</v>
       </c>
       <c r="E73" t="n">
         <v>1.1238</v>
@@ -3814,7 +3814,7 @@
         <v>0.8421</v>
       </c>
       <c r="D74" t="n">
-        <v>0.0277</v>
+        <v>-0.001</v>
       </c>
       <c r="E74" t="n">
         <v>1.1116</v>
@@ -3860,7 +3860,7 @@
         <v>0.8419</v>
       </c>
       <c r="D75" t="n">
-        <v>0.0276</v>
+        <v>-0.0011</v>
       </c>
       <c r="E75" t="n">
         <v>1.1114</v>
@@ -3906,7 +3906,7 @@
         <v>0.82</v>
       </c>
       <c r="D76" t="n">
-        <v>0.0159</v>
+        <v>-0.0126</v>
       </c>
       <c r="E76" t="n">
         <v>1.0825</v>
@@ -3952,7 +3952,7 @@
         <v>0.8125</v>
       </c>
       <c r="D77" t="n">
-        <v>0.0119</v>
+        <v>-0.0166</v>
       </c>
       <c r="E77" t="n">
         <v>1.0726</v>
@@ -3998,7 +3998,7 @@
         <v>0.7887999999999999</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.0007</v>
+        <v>-0.0291</v>
       </c>
       <c r="E78" t="n">
         <v>1.0413</v>
@@ -4038,25 +4038,25 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1.0403</v>
+        <v>1.0325</v>
       </c>
       <c r="C79" t="n">
-        <v>0.7881</v>
+        <v>0.7822</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.0011</v>
+        <v>-0.0326</v>
       </c>
       <c r="E79" t="n">
-        <v>1.0403</v>
+        <v>1.0325</v>
       </c>
       <c r="F79" t="n">
-        <v>1.0403</v>
+        <v>1.0325</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>1.0403</v>
+        <v>1.0325</v>
       </c>
       <c r="I79" t="n">
         <v>1.05</v>
@@ -4090,7 +4090,7 @@
         <v>0.7709</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.0103</v>
+        <v>-0.0385</v>
       </c>
       <c r="E80" t="n">
         <v>1.0176</v>
@@ -4136,7 +4136,7 @@
         <v>0.7631</v>
       </c>
       <c r="D81" t="n">
-        <v>-0.0144</v>
+        <v>-0.0426</v>
       </c>
       <c r="E81" t="n">
         <v>1.0073</v>
@@ -4176,25 +4176,25 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.9797</v>
+        <v>0.9761</v>
       </c>
       <c r="C82" t="n">
-        <v>0.7422</v>
+        <v>0.7393999999999999</v>
       </c>
       <c r="D82" t="n">
-        <v>-0.0256</v>
+        <v>-0.055</v>
       </c>
       <c r="E82" t="n">
-        <v>0.9797</v>
+        <v>0.9761</v>
       </c>
       <c r="F82" t="n">
-        <v>0.9797</v>
+        <v>0.9761</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0.9797</v>
+        <v>0.9761</v>
       </c>
       <c r="I82" t="n">
         <v>0.9843</v>
@@ -4228,7 +4228,7 @@
         <v>0.7291</v>
       </c>
       <c r="D83" t="n">
-        <v>-0.0326</v>
+        <v>-0.0605</v>
       </c>
       <c r="E83" t="n">
         <v>0.9624</v>
@@ -4268,25 +4268,25 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.9602000000000001</v>
+        <v>0.9477</v>
       </c>
       <c r="C84" t="n">
-        <v>0.7274</v>
+        <v>0.7179</v>
       </c>
       <c r="D84" t="n">
-        <v>-0.0335</v>
+        <v>-0.0663</v>
       </c>
       <c r="E84" t="n">
-        <v>0.9602000000000001</v>
+        <v>0.9477</v>
       </c>
       <c r="F84" t="n">
-        <v>0.8469</v>
+        <v>0.8344</v>
       </c>
       <c r="G84" t="n">
         <v>0.1133</v>
       </c>
       <c r="H84" t="n">
-        <v>0.8469</v>
+        <v>0.8344</v>
       </c>
       <c r="I84" t="n">
         <v>0.8628</v>
@@ -4314,25 +4314,25 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.8586</v>
+        <v>0.8522</v>
       </c>
       <c r="C85" t="n">
-        <v>0.6504</v>
+        <v>0.6456</v>
       </c>
       <c r="D85" t="n">
-        <v>-0.0745</v>
+        <v>-0.1044</v>
       </c>
       <c r="E85" t="n">
-        <v>0.8586</v>
+        <v>0.8522</v>
       </c>
       <c r="F85" t="n">
-        <v>0.8586</v>
+        <v>0.8522</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>0.8586</v>
+        <v>0.8522</v>
       </c>
       <c r="I85" t="n">
         <v>0.8666</v>
@@ -4366,7 +4366,7 @@
         <v>0.6032999999999999</v>
       </c>
       <c r="D86" t="n">
-        <v>-0.09959999999999999</v>
+        <v>-0.1266</v>
       </c>
       <c r="E86" t="n">
         <v>0.7964</v>
@@ -4412,7 +4412,7 @@
         <v>0.4623</v>
       </c>
       <c r="D87" t="n">
-        <v>-0.1748</v>
+        <v>-0.2008</v>
       </c>
       <c r="E87" t="n">
         <v>0.6103</v>
@@ -4458,7 +4458,7 @@
         <v>0.4382</v>
       </c>
       <c r="D88" t="n">
-        <v>-0.1877</v>
+        <v>-0.2134</v>
       </c>
       <c r="E88" t="n">
         <v>0.5785</v>
@@ -4504,7 +4504,7 @@
         <v>0.418</v>
       </c>
       <c r="D89" t="n">
-        <v>-0.1984</v>
+        <v>-0.2241</v>
       </c>
       <c r="E89" t="n">
         <v>0.5518</v>
@@ -4550,7 +4550,7 @@
         <v>0.4123</v>
       </c>
       <c r="D90" t="n">
-        <v>-0.2015</v>
+        <v>-0.2271</v>
       </c>
       <c r="E90" t="n">
         <v>0.5442</v>
@@ -4596,7 +4596,7 @@
         <v>0.3951</v>
       </c>
       <c r="D91" t="n">
-        <v>-0.2107</v>
+        <v>-0.2361</v>
       </c>
       <c r="E91" t="n">
         <v>0.5215</v>
@@ -4642,7 +4642,7 @@
         <v>0.3668</v>
       </c>
       <c r="D92" t="n">
-        <v>-0.2258</v>
+        <v>-0.251</v>
       </c>
       <c r="E92" t="n">
         <v>0.4842</v>
@@ -4682,25 +4682,25 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.4732</v>
+        <v>0.4697</v>
       </c>
       <c r="C93" t="n">
-        <v>0.3585</v>
+        <v>0.3558</v>
       </c>
       <c r="D93" t="n">
-        <v>-0.2302</v>
+        <v>-0.2568</v>
       </c>
       <c r="E93" t="n">
-        <v>0.4732</v>
+        <v>0.4697</v>
       </c>
       <c r="F93" t="n">
-        <v>0.4732</v>
+        <v>0.4697</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>0.4732</v>
+        <v>0.4697</v>
       </c>
       <c r="I93" t="n">
         <v>0.4777</v>
@@ -4734,7 +4734,7 @@
         <v>0.3557</v>
       </c>
       <c r="D94" t="n">
-        <v>-0.2317</v>
+        <v>-0.2568</v>
       </c>
       <c r="E94" t="n">
         <v>0.4696</v>
@@ -4780,7 +4780,7 @@
         <v>0.3505</v>
       </c>
       <c r="D95" t="n">
-        <v>-0.2344</v>
+        <v>-0.2596</v>
       </c>
       <c r="E95" t="n">
         <v>0.4627</v>
@@ -4826,7 +4826,7 @@
         <v>0.3337</v>
       </c>
       <c r="D96" t="n">
-        <v>-0.2434</v>
+        <v>-0.2684</v>
       </c>
       <c r="E96" t="n">
         <v>0.4405</v>
@@ -4872,7 +4872,7 @@
         <v>0.3253</v>
       </c>
       <c r="D97" t="n">
-        <v>-0.2479</v>
+        <v>-0.2728</v>
       </c>
       <c r="E97" t="n">
         <v>0.4294</v>
@@ -4918,7 +4918,7 @@
         <v>0.3126</v>
       </c>
       <c r="D98" t="n">
-        <v>-0.2546</v>
+        <v>-0.2795</v>
       </c>
       <c r="E98" t="n">
         <v>0.4127</v>
@@ -4964,7 +4964,7 @@
         <v>0.2997</v>
       </c>
       <c r="D99" t="n">
-        <v>-0.2615</v>
+        <v>-0.2863</v>
       </c>
       <c r="E99" t="n">
         <v>0.3956</v>
@@ -5010,7 +5010,7 @@
         <v>0.2857</v>
       </c>
       <c r="D100" t="n">
-        <v>-0.269</v>
+        <v>-0.2936</v>
       </c>
       <c r="E100" t="n">
         <v>0.3772</v>
@@ -5056,7 +5056,7 @@
         <v>0.28</v>
       </c>
       <c r="D101" t="n">
-        <v>-0.2721</v>
+        <v>-0.2967</v>
       </c>
       <c r="E101" t="n">
         <v>0.3696</v>
@@ -5102,7 +5102,7 @@
         <v>0.2792</v>
       </c>
       <c r="D102" t="n">
-        <v>-0.2725</v>
+        <v>-0.2971</v>
       </c>
       <c r="E102" t="n">
         <v>0.3685</v>
@@ -5142,25 +5142,25 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.3653</v>
+        <v>0.3626</v>
       </c>
       <c r="C103" t="n">
-        <v>0.2767</v>
+        <v>0.2747</v>
       </c>
       <c r="D103" t="n">
-        <v>-0.2738</v>
+        <v>-0.2995</v>
       </c>
       <c r="E103" t="n">
-        <v>0.3653</v>
+        <v>0.3626</v>
       </c>
       <c r="F103" t="n">
-        <v>0.3653</v>
+        <v>0.3626</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>0.3653</v>
+        <v>0.3626</v>
       </c>
       <c r="I103" t="n">
         <v>0.3687</v>
@@ -5194,7 +5194,7 @@
         <v>0.2718</v>
       </c>
       <c r="D104" t="n">
-        <v>-0.2764</v>
+        <v>-0.301</v>
       </c>
       <c r="E104" t="n">
         <v>0.3588</v>
@@ -5234,25 +5234,25 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.2955</v>
+        <v>0.2933</v>
       </c>
       <c r="C105" t="n">
-        <v>0.2239</v>
+        <v>0.2222</v>
       </c>
       <c r="D105" t="n">
-        <v>-0.302</v>
+        <v>-0.3271</v>
       </c>
       <c r="E105" t="n">
-        <v>0.2955</v>
+        <v>0.2933</v>
       </c>
       <c r="F105" t="n">
-        <v>0.2955</v>
+        <v>0.2933</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>0.2955</v>
+        <v>0.2933</v>
       </c>
       <c r="I105" t="n">
         <v>0.2983</v>
@@ -5286,7 +5286,7 @@
         <v>0.2117</v>
       </c>
       <c r="D106" t="n">
-        <v>-0.3085</v>
+        <v>-0.3326</v>
       </c>
       <c r="E106" t="n">
         <v>0.2794</v>
@@ -5332,7 +5332,7 @@
         <v>0.1926</v>
       </c>
       <c r="D107" t="n">
-        <v>-0.3186</v>
+        <v>-0.3426</v>
       </c>
       <c r="E107" t="n">
         <v>0.2543</v>
@@ -5372,25 +5372,25 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.0644</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="C108" t="n">
-        <v>0.0488</v>
+        <v>0.0483</v>
       </c>
       <c r="D108" t="n">
-        <v>-0.3953</v>
+        <v>-0.4185</v>
       </c>
       <c r="E108" t="n">
-        <v>0.0644</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="F108" t="n">
-        <v>0.0644</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>0.0644</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="I108" t="n">
         <v>0.0653</v>
@@ -5418,25 +5418,25 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>-0.061</v>
+        <v>-0.0608</v>
       </c>
       <c r="C109" t="n">
-        <v>-0.0462</v>
+        <v>-0.0461</v>
       </c>
       <c r="D109" t="n">
-        <v>-0.446</v>
+        <v>-0.4681</v>
       </c>
       <c r="E109" t="n">
-        <v>-0.061</v>
+        <v>-0.0608</v>
       </c>
       <c r="F109" t="n">
-        <v>-0.061</v>
+        <v>-0.0608</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
       </c>
       <c r="H109" t="n">
-        <v>-0.061</v>
+        <v>-0.0608</v>
       </c>
       <c r="I109" t="n">
         <v>-0.0613</v>
@@ -5470,7 +5470,7 @@
         <v>-0.2078</v>
       </c>
       <c r="D110" t="n">
-        <v>-0.5322</v>
+        <v>-0.5532</v>
       </c>
       <c r="E110" t="n">
         <v>-0.2743</v>
@@ -5516,7 +5516,7 @@
         <v>-0.2297</v>
       </c>
       <c r="D111" t="n">
-        <v>-0.5438</v>
+        <v>-0.5647</v>
       </c>
       <c r="E111" t="n">
         <v>-0.3032</v>
@@ -5562,7 +5562,7 @@
         <v>-0.245</v>
       </c>
       <c r="D112" t="n">
-        <v>-0.552</v>
+        <v>-0.5728</v>
       </c>
       <c r="E112" t="n">
         <v>-0.3234</v>
@@ -5608,7 +5608,7 @@
         <v>-0.2657</v>
       </c>
       <c r="D113" t="n">
-        <v>-0.5629999999999999</v>
+        <v>-0.5836</v>
       </c>
       <c r="E113" t="n">
         <v>-0.3507</v>
@@ -5654,7 +5654,7 @@
         <v>-0.2921</v>
       </c>
       <c r="D114" t="n">
-        <v>-0.5770999999999999</v>
+        <v>-0.5975</v>
       </c>
       <c r="E114" t="n">
         <v>-0.3856</v>
@@ -5690,93 +5690,93 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Calyx</t>
+          <t>Vexite</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>-0.4128</v>
+        <v>-0.4153</v>
       </c>
       <c r="C115" t="n">
-        <v>-0.3127</v>
+        <v>-0.3146</v>
       </c>
       <c r="D115" t="n">
-        <v>-0.5881</v>
+        <v>-0.6094000000000001</v>
       </c>
       <c r="E115" t="n">
-        <v>-0.4128</v>
+        <v>-0.4153</v>
       </c>
       <c r="F115" t="n">
-        <v>0.5872000000000001</v>
+        <v>-0.4153</v>
       </c>
       <c r="G115" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>0.5872000000000001</v>
+        <v>-0.4153</v>
       </c>
       <c r="I115" t="n">
-        <v>0.5982</v>
+        <v>-0.4153</v>
       </c>
       <c r="J115" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K115" t="n">
-        <v>381</v>
+        <v>248</v>
       </c>
       <c r="L115" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>-0.4018</v>
+        <v>-0.4153</v>
       </c>
       <c r="N115" t="n">
-        <v>430</v>
+        <v>248</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Vexite</t>
+          <t>Calyx</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>-0.4153</v>
+        <v>-0.4215</v>
       </c>
       <c r="C116" t="n">
-        <v>-0.3146</v>
+        <v>-0.3193</v>
       </c>
       <c r="D116" t="n">
-        <v>-0.5891</v>
+        <v>-0.6118</v>
       </c>
       <c r="E116" t="n">
-        <v>-0.4153</v>
+        <v>-0.4215</v>
       </c>
       <c r="F116" t="n">
-        <v>-0.4153</v>
+        <v>0.5785</v>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H116" t="n">
-        <v>-0.4153</v>
+        <v>0.5785</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4153</v>
+        <v>0.5982</v>
       </c>
       <c r="J116" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K116" t="n">
-        <v>248</v>
+        <v>381</v>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M116" t="n">
-        <v>-0.4153</v>
+        <v>-0.4018</v>
       </c>
       <c r="N116" t="n">
-        <v>248</v>
+        <v>430</v>
       </c>
     </row>
     <row r="117">
@@ -5792,7 +5792,7 @@
         <v>-0.3206</v>
       </c>
       <c r="D117" t="n">
-        <v>-0.5923</v>
+        <v>-0.6125</v>
       </c>
       <c r="E117" t="n">
         <v>-0.4232</v>
@@ -5838,7 +5838,7 @@
         <v>-0.3317</v>
       </c>
       <c r="D118" t="n">
-        <v>-0.5983000000000001</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="E118" t="n">
         <v>-0.4379</v>
@@ -5884,7 +5884,7 @@
         <v>-0.3616</v>
       </c>
       <c r="D119" t="n">
-        <v>-0.6142</v>
+        <v>-0.6341</v>
       </c>
       <c r="E119" t="n">
         <v>-0.4774</v>
@@ -5930,7 +5930,7 @@
         <v>-0.3766</v>
       </c>
       <c r="D120" t="n">
-        <v>-0.6222</v>
+        <v>-0.642</v>
       </c>
       <c r="E120" t="n">
         <v>-0.4972</v>
@@ -5976,7 +5976,7 @@
         <v>-0.4254</v>
       </c>
       <c r="D121" t="n">
-        <v>-0.6482</v>
+        <v>-0.6677</v>
       </c>
       <c r="E121" t="n">
         <v>-0.5616</v>
@@ -6022,7 +6022,7 @@
         <v>-0.459</v>
       </c>
       <c r="D122" t="n">
-        <v>-0.6661</v>
+        <v>-0.6853</v>
       </c>
       <c r="E122" t="n">
         <v>-0.6059</v>
@@ -6068,7 +6068,7 @@
         <v>-0.4855</v>
       </c>
       <c r="D123" t="n">
-        <v>-0.6803</v>
+        <v>-0.6992</v>
       </c>
       <c r="E123" t="n">
         <v>-0.6409</v>
@@ -6104,139 +6104,139 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>exit</t>
+          <t>n0rb3r7</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>-0.6566</v>
+        <v>-0.6528</v>
       </c>
       <c r="C124" t="n">
-        <v>-0.4974</v>
+        <v>-0.4945</v>
       </c>
       <c r="D124" t="n">
-        <v>-0.6866</v>
+        <v>-0.704</v>
       </c>
       <c r="E124" t="n">
-        <v>-0.6566</v>
+        <v>-0.6528</v>
       </c>
       <c r="F124" t="n">
-        <v>-0.6566</v>
+        <v>-0.6528</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>-0.6566</v>
+        <v>-0.6528</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.6597</v>
+        <v>-0.6637999999999999</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
       </c>
       <c r="K124" t="n">
-        <v>456</v>
+        <v>382</v>
       </c>
       <c r="L124" t="n">
         <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>-0.6597</v>
+        <v>-0.6637999999999999</v>
       </c>
       <c r="N124" t="n">
-        <v>456</v>
+        <v>382</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Snappi</t>
+          <t>exit</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>-0.6568000000000001</v>
+        <v>-0.6542</v>
       </c>
       <c r="C125" t="n">
-        <v>-0.4975</v>
+        <v>-0.4956</v>
       </c>
       <c r="D125" t="n">
-        <v>-0.6867</v>
+        <v>-0.7045</v>
       </c>
       <c r="E125" t="n">
-        <v>-0.6568000000000001</v>
+        <v>-0.6542</v>
       </c>
       <c r="F125" t="n">
-        <v>-1.0185</v>
+        <v>-0.6542</v>
       </c>
       <c r="G125" t="n">
-        <v>0.3617</v>
+        <v>0</v>
       </c>
       <c r="H125" t="n">
-        <v>-1.0185</v>
+        <v>-0.6542</v>
       </c>
       <c r="I125" t="n">
-        <v>-1.0185</v>
+        <v>-0.6597</v>
       </c>
       <c r="J125" t="n">
-        <v>0.3617</v>
+        <v>0</v>
       </c>
       <c r="K125" t="n">
-        <v>240</v>
+        <v>456</v>
       </c>
       <c r="L125" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>-0.6567999999999999</v>
+        <v>-0.6597</v>
       </c>
       <c r="N125" t="n">
-        <v>359</v>
+        <v>456</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>n0rb3r7</t>
+          <t>Snappi</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>-0.6577</v>
+        <v>-0.6568000000000001</v>
       </c>
       <c r="C126" t="n">
-        <v>-0.4982</v>
+        <v>-0.4975</v>
       </c>
       <c r="D126" t="n">
-        <v>-0.6871</v>
+        <v>-0.7056</v>
       </c>
       <c r="E126" t="n">
-        <v>-0.6577</v>
+        <v>-0.6568000000000001</v>
       </c>
       <c r="F126" t="n">
-        <v>-0.6577</v>
+        <v>-1.0185</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>0.3617</v>
       </c>
       <c r="H126" t="n">
-        <v>-0.6577</v>
+        <v>-1.0185</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.6637999999999999</v>
+        <v>-1.0185</v>
       </c>
       <c r="J126" t="n">
-        <v>0</v>
+        <v>0.3617</v>
       </c>
       <c r="K126" t="n">
-        <v>382</v>
+        <v>240</v>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="M126" t="n">
-        <v>-0.6637999999999999</v>
+        <v>-0.6567999999999999</v>
       </c>
       <c r="N126" t="n">
-        <v>382</v>
+        <v>359</v>
       </c>
     </row>
     <row r="127">
@@ -6252,7 +6252,7 @@
         <v>-0.5433</v>
       </c>
       <c r="D127" t="n">
-        <v>-0.7111</v>
+        <v>-0.7296</v>
       </c>
       <c r="E127" t="n">
         <v>-0.7171999999999999</v>
@@ -6298,7 +6298,7 @@
         <v>-0.604</v>
       </c>
       <c r="D128" t="n">
-        <v>-0.7435</v>
+        <v>-0.7616000000000001</v>
       </c>
       <c r="E128" t="n">
         <v>-0.7973</v>
@@ -6344,7 +6344,7 @@
         <v>-0.6574</v>
       </c>
       <c r="D129" t="n">
-        <v>-0.7719</v>
+        <v>-0.7896</v>
       </c>
       <c r="E129" t="n">
         <v>-0.8678</v>
@@ -6390,7 +6390,7 @@
         <v>-0.6706</v>
       </c>
       <c r="D130" t="n">
-        <v>-0.779</v>
+        <v>-0.7966</v>
       </c>
       <c r="E130" t="n">
         <v>-0.8853</v>
@@ -6436,7 +6436,7 @@
         <v>-0.6819</v>
       </c>
       <c r="D131" t="n">
-        <v>-0.785</v>
+        <v>-0.8025</v>
       </c>
       <c r="E131" t="n">
         <v>-0.9001</v>
@@ -6482,7 +6482,7 @@
         <v>-0.6975</v>
       </c>
       <c r="D132" t="n">
-        <v>-0.7933</v>
+        <v>-0.8107</v>
       </c>
       <c r="E132" t="n">
         <v>-0.9207</v>
@@ -6528,7 +6528,7 @@
         <v>-0.7056</v>
       </c>
       <c r="D133" t="n">
-        <v>-0.7976</v>
+        <v>-0.8149999999999999</v>
       </c>
       <c r="E133" t="n">
         <v>-0.9314</v>
@@ -6574,7 +6574,7 @@
         <v>-0.7213000000000001</v>
       </c>
       <c r="D134" t="n">
-        <v>-0.806</v>
+        <v>-0.8233</v>
       </c>
       <c r="E134" t="n">
         <v>-0.9522</v>
@@ -6620,7 +6620,7 @@
         <v>-0.7456</v>
       </c>
       <c r="D135" t="n">
-        <v>-0.819</v>
+        <v>-0.8361</v>
       </c>
       <c r="E135" t="n">
         <v>-0.9843</v>
@@ -6666,7 +6666,7 @@
         <v>-0.7732</v>
       </c>
       <c r="D136" t="n">
-        <v>-0.8337</v>
+        <v>-0.8506</v>
       </c>
       <c r="E136" t="n">
         <v>-1.0207</v>
@@ -6712,7 +6712,7 @@
         <v>-0.7735</v>
       </c>
       <c r="D137" t="n">
-        <v>-0.8339</v>
+        <v>-0.8507</v>
       </c>
       <c r="E137" t="n">
         <v>-1.0211</v>
@@ -6758,7 +6758,7 @@
         <v>-0.8868</v>
       </c>
       <c r="D138" t="n">
-        <v>-0.8943</v>
+        <v>-0.9103</v>
       </c>
       <c r="E138" t="n">
         <v>-1.1706</v>
@@ -6804,7 +6804,7 @@
         <v>-0.8913</v>
       </c>
       <c r="D139" t="n">
-        <v>-0.8967000000000001</v>
+        <v>-0.9127</v>
       </c>
       <c r="E139" t="n">
         <v>-1.1766</v>
@@ -6850,7 +6850,7 @@
         <v>-1.0029</v>
       </c>
       <c r="D140" t="n">
-        <v>-0.9562</v>
+        <v>-0.9714</v>
       </c>
       <c r="E140" t="n">
         <v>-1.3239</v>
@@ -6886,93 +6886,93 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Sico</t>
+          <t>roeJ</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>-1.4354</v>
+        <v>-1.4327</v>
       </c>
       <c r="C141" t="n">
-        <v>-1.0874</v>
+        <v>-1.0853</v>
       </c>
       <c r="D141" t="n">
-        <v>-1.0012</v>
+        <v>-1.0147</v>
       </c>
       <c r="E141" t="n">
-        <v>-1.4354</v>
+        <v>-1.4327</v>
       </c>
       <c r="F141" t="n">
-        <v>-1.4354</v>
+        <v>-1.4327</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
       </c>
       <c r="H141" t="n">
-        <v>-1.4354</v>
+        <v>-1.4327</v>
       </c>
       <c r="I141" t="n">
-        <v>-1.4354</v>
+        <v>-1.4569</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
       </c>
       <c r="K141" t="n">
-        <v>248</v>
+        <v>377</v>
       </c>
       <c r="L141" t="n">
         <v>0</v>
       </c>
       <c r="M141" t="n">
-        <v>-1.4354</v>
+        <v>-1.4569</v>
       </c>
       <c r="N141" t="n">
-        <v>248</v>
+        <v>377</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>roeJ</t>
+          <t>Sico</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>-1.4434</v>
+        <v>-1.4354</v>
       </c>
       <c r="C142" t="n">
-        <v>-1.0934</v>
+        <v>-1.0874</v>
       </c>
       <c r="D142" t="n">
-        <v>-1.0045</v>
+        <v>-1.0158</v>
       </c>
       <c r="E142" t="n">
-        <v>-1.4434</v>
+        <v>-1.4354</v>
       </c>
       <c r="F142" t="n">
-        <v>-1.4434</v>
+        <v>-1.4354</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
       </c>
       <c r="H142" t="n">
-        <v>-1.4434</v>
+        <v>-1.4354</v>
       </c>
       <c r="I142" t="n">
-        <v>-1.4569</v>
+        <v>-1.4354</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
       </c>
       <c r="K142" t="n">
-        <v>377</v>
+        <v>248</v>
       </c>
       <c r="L142" t="n">
         <v>0</v>
       </c>
       <c r="M142" t="n">
-        <v>-1.4569</v>
+        <v>-1.4354</v>
       </c>
       <c r="N142" t="n">
-        <v>377</v>
+        <v>248</v>
       </c>
     </row>
     <row r="143">
@@ -6988,7 +6988,7 @@
         <v>-1.1665</v>
       </c>
       <c r="D143" t="n">
-        <v>-1.0434</v>
+        <v>-1.0574</v>
       </c>
       <c r="E143" t="n">
         <v>-1.5398</v>
@@ -7034,7 +7034,7 @@
         <v>-1.1831</v>
       </c>
       <c r="D144" t="n">
-        <v>-1.0523</v>
+        <v>-1.0661</v>
       </c>
       <c r="E144" t="n">
         <v>-1.5618</v>
@@ -7080,7 +7080,7 @@
         <v>-1.1896</v>
       </c>
       <c r="D145" t="n">
-        <v>-1.0558</v>
+        <v>-1.0696</v>
       </c>
       <c r="E145" t="n">
         <v>-1.5704</v>
@@ -7126,7 +7126,7 @@
         <v>-1.1907</v>
       </c>
       <c r="D146" t="n">
-        <v>-1.0563</v>
+        <v>-1.0701</v>
       </c>
       <c r="E146" t="n">
         <v>-1.5718</v>
@@ -7172,7 +7172,7 @@
         <v>-1.2073</v>
       </c>
       <c r="D147" t="n">
-        <v>-1.0652</v>
+        <v>-1.0788</v>
       </c>
       <c r="E147" t="n">
         <v>-1.5937</v>
@@ -7218,7 +7218,7 @@
         <v>-1.2834</v>
       </c>
       <c r="D148" t="n">
-        <v>-1.1058</v>
+        <v>-1.1189</v>
       </c>
       <c r="E148" t="n">
         <v>-1.6942</v>
@@ -7264,7 +7264,7 @@
         <v>-1.305</v>
       </c>
       <c r="D149" t="n">
-        <v>-1.1173</v>
+        <v>-1.1302</v>
       </c>
       <c r="E149" t="n">
         <v>-1.7227</v>
@@ -7310,7 +7310,7 @@
         <v>-1.3785</v>
       </c>
       <c r="D150" t="n">
-        <v>-1.1565</v>
+        <v>-1.1689</v>
       </c>
       <c r="E150" t="n">
         <v>-1.8197</v>
@@ -7356,7 +7356,7 @@
         <v>-1.3804</v>
       </c>
       <c r="D151" t="n">
-        <v>-1.1575</v>
+        <v>-1.1699</v>
       </c>
       <c r="E151" t="n">
         <v>-1.8222</v>
@@ -7402,7 +7402,7 @@
         <v>-1.497</v>
       </c>
       <c r="D152" t="n">
-        <v>-1.2197</v>
+        <v>-1.2312</v>
       </c>
       <c r="E152" t="n">
         <v>-1.9762</v>
@@ -7448,7 +7448,7 @@
         <v>-1.5184</v>
       </c>
       <c r="D153" t="n">
-        <v>-1.2311</v>
+        <v>-1.2425</v>
       </c>
       <c r="E153" t="n">
         <v>-2.0044</v>
@@ -7494,7 +7494,7 @@
         <v>-1.7363</v>
       </c>
       <c r="D154" t="n">
-        <v>-1.3473</v>
+        <v>-1.3571</v>
       </c>
       <c r="E154" t="n">
         <v>-2.2921</v>
@@ -7540,7 +7540,7 @@
         <v>-2.0463</v>
       </c>
       <c r="D155" t="n">
-        <v>-1.5126</v>
+        <v>-1.5201</v>
       </c>
       <c r="E155" t="n">
         <v>-2.7012</v>
@@ -7586,7 +7586,7 @@
         <v>-2.0766</v>
       </c>
       <c r="D156" t="n">
-        <v>-1.5287</v>
+        <v>-1.536</v>
       </c>
       <c r="E156" t="n">
         <v>-2.7412</v>
@@ -7622,93 +7622,93 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ADK</t>
+          <t>MAJ3R</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>-2.9266</v>
+        <v>-2.8876</v>
       </c>
       <c r="C157" t="n">
-        <v>-2.217</v>
+        <v>-2.1875</v>
       </c>
       <c r="D157" t="n">
-        <v>-1.6036</v>
+        <v>-1.5943</v>
       </c>
       <c r="E157" t="n">
-        <v>-2.9266</v>
+        <v>-2.8876</v>
       </c>
       <c r="F157" t="n">
-        <v>-2.9266</v>
+        <v>-2.9797</v>
       </c>
       <c r="G157" t="n">
-        <v>0</v>
+        <v>0.0921</v>
       </c>
       <c r="H157" t="n">
-        <v>-2.9266</v>
+        <v>-2.9797</v>
       </c>
       <c r="I157" t="n">
-        <v>-2.9266</v>
+        <v>-3.0813</v>
       </c>
       <c r="J157" t="n">
-        <v>0</v>
+        <v>0.0921</v>
       </c>
       <c r="K157" t="n">
-        <v>162</v>
+        <v>381</v>
       </c>
       <c r="L157" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M157" t="n">
-        <v>-2.9266</v>
+        <v>-2.9892</v>
       </c>
       <c r="N157" t="n">
-        <v>162</v>
+        <v>430</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>MAJ3R</t>
+          <t>ADK</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>-2.9325</v>
+        <v>-2.9266</v>
       </c>
       <c r="C158" t="n">
-        <v>-2.2215</v>
+        <v>-2.217</v>
       </c>
       <c r="D158" t="n">
-        <v>-1.606</v>
+        <v>-1.6099</v>
       </c>
       <c r="E158" t="n">
-        <v>-2.9325</v>
+        <v>-2.9266</v>
       </c>
       <c r="F158" t="n">
-        <v>-3.0246</v>
+        <v>-2.9266</v>
       </c>
       <c r="G158" t="n">
-        <v>0.0921</v>
+        <v>0</v>
       </c>
       <c r="H158" t="n">
-        <v>-3.0246</v>
+        <v>-2.9266</v>
       </c>
       <c r="I158" t="n">
-        <v>-3.0813</v>
+        <v>-2.9266</v>
       </c>
       <c r="J158" t="n">
-        <v>0.0921</v>
+        <v>0</v>
       </c>
       <c r="K158" t="n">
-        <v>381</v>
+        <v>162</v>
       </c>
       <c r="L158" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M158" t="n">
-        <v>-2.9892</v>
+        <v>-2.9266</v>
       </c>
       <c r="N158" t="n">
-        <v>430</v>
+        <v>162</v>
       </c>
     </row>
     <row r="159">
@@ -7724,7 +7724,7 @@
         <v>-2.2595</v>
       </c>
       <c r="D159" t="n">
-        <v>-1.6263</v>
+        <v>-1.6322</v>
       </c>
       <c r="E159" t="n">
         <v>-2.9827</v>
@@ -7764,25 +7764,25 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>-4.491</v>
+        <v>-4.4576</v>
       </c>
       <c r="C160" t="n">
-        <v>-3.4021</v>
+        <v>-3.3768</v>
       </c>
       <c r="D160" t="n">
-        <v>-2.2356</v>
+        <v>-2.2198</v>
       </c>
       <c r="E160" t="n">
-        <v>-4.491</v>
+        <v>-4.4576</v>
       </c>
       <c r="F160" t="n">
-        <v>-4.491</v>
+        <v>-4.4576</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
       </c>
       <c r="H160" t="n">
-        <v>-4.491</v>
+        <v>-4.4576</v>
       </c>
       <c r="I160" t="n">
         <v>-4.5329</v>
@@ -7816,7 +7816,7 @@
         <v>-3.8428</v>
       </c>
       <c r="D161" t="n">
-        <v>-2.4707</v>
+        <v>-2.4649</v>
       </c>
       <c r="E161" t="n">
         <v>-5.0728</v>
